--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{932A2BBF-6A0D-401F-991D-AE0312935962}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FF282D-1CA7-402A-8F41-22755B57E017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="3735" windowWidth="19200" windowHeight="10335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="491">
   <si>
     <t>商品名称</t>
   </si>
@@ -1763,6 +1763,18 @@
   </si>
   <si>
     <t>6901028318549</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>太少（颜悦）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028155557</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028155540</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5221,14 +5233,26 @@
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126" s="21"/>
-      <c r="B126" s="18"/>
-      <c r="C126" s="18"/>
+      <c r="A126" s="21" t="s">
+        <v>488</v>
+      </c>
+      <c r="B126" s="18">
+        <v>167</v>
+      </c>
+      <c r="C126" s="18">
+        <v>200</v>
+      </c>
       <c r="D126" s="18"/>
-      <c r="E126" s="18"/>
+      <c r="E126" s="18">
+        <v>20</v>
+      </c>
       <c r="F126" s="18"/>
-      <c r="G126" s="19"/>
-      <c r="H126" s="19"/>
+      <c r="G126" s="19" t="s">
+        <v>489</v>
+      </c>
+      <c r="H126" s="19" t="s">
+        <v>490</v>
+      </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="21"/>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9FF282D-1CA7-402A-8F41-22755B57E017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD84B85-BD63-4EA8-BC8F-61F39925E59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="3735" windowWidth="19200" windowHeight="10335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1766,15 +1766,15 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>太少（颜悦）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>6901028155557</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
     <t>6901028155540</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰山（颜悦）</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5234,10 +5234,10 @@
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="21" t="s">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="B126" s="18">
-        <v>167</v>
+        <v>167.48</v>
       </c>
       <c r="C126" s="18">
         <v>200</v>
@@ -5248,10 +5248,10 @@
       </c>
       <c r="F126" s="18"/>
       <c r="G126" s="19" t="s">
+        <v>488</v>
+      </c>
+      <c r="H126" s="19" t="s">
         <v>489</v>
-      </c>
-      <c r="H126" s="19" t="s">
-        <v>490</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7FD84B85-BD63-4EA8-BC8F-61F39925E59F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEE6234-9254-479D-B56F-9AA9219E8AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="3735" windowWidth="19200" windowHeight="10335" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="690" uniqueCount="491">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="494">
   <si>
     <t>商品名称</t>
   </si>
@@ -1775,6 +1775,18 @@
   </si>
   <si>
     <t>泰山（颜悦）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>泰山（心悦）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028159753</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028159764</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5255,14 +5267,26 @@
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" s="21"/>
-      <c r="B127" s="18"/>
-      <c r="C127" s="18"/>
+      <c r="A127" s="21" t="s">
+        <v>491</v>
+      </c>
+      <c r="B127" s="18">
+        <v>139.91999999999999</v>
+      </c>
+      <c r="C127" s="18">
+        <v>160</v>
+      </c>
       <c r="D127" s="18"/>
-      <c r="E127" s="18"/>
+      <c r="E127" s="18">
+        <v>16</v>
+      </c>
       <c r="F127" s="18"/>
-      <c r="G127" s="19"/>
-      <c r="H127" s="19"/>
+      <c r="G127" s="19" t="s">
+        <v>492</v>
+      </c>
+      <c r="H127" s="19" t="s">
+        <v>493</v>
+      </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="21"/>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BEE6234-9254-479D-B56F-9AA9219E8AF0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A4D219-BCFB-4495-86D8-86729423F9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="693" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="497">
   <si>
     <t>商品名称</t>
   </si>
@@ -1787,6 +1787,18 @@
   </si>
   <si>
     <t>6901028159764</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>芙蓉王（硬红带细支）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028201995</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028201988</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2245,7 +2257,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80C0A3B-2542-45F0-B3D4-3E8698F6D850}">
-  <dimension ref="A1:K132"/>
+  <dimension ref="A1:K135"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5289,14 +5301,26 @@
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128" s="21"/>
-      <c r="B128" s="18"/>
-      <c r="C128" s="18"/>
+      <c r="A128" s="21" t="s">
+        <v>494</v>
+      </c>
+      <c r="B128" s="18">
+        <v>263</v>
+      </c>
+      <c r="C128" s="18">
+        <v>300</v>
+      </c>
       <c r="D128" s="18"/>
-      <c r="E128" s="18"/>
+      <c r="E128" s="18">
+        <v>30</v>
+      </c>
       <c r="F128" s="18"/>
-      <c r="G128" s="19"/>
-      <c r="H128" s="19"/>
+      <c r="G128" s="19" t="s">
+        <v>495</v>
+      </c>
+      <c r="H128" s="19" t="s">
+        <v>496</v>
+      </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="21"/>
@@ -5338,6 +5362,36 @@
       <c r="G132" s="19"/>
       <c r="H132" s="19"/>
     </row>
+    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A133" s="21"/>
+      <c r="B133" s="18"/>
+      <c r="C133" s="18"/>
+      <c r="D133" s="18"/>
+      <c r="E133" s="18"/>
+      <c r="F133" s="18"/>
+      <c r="G133" s="19"/>
+      <c r="H133" s="19"/>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A134" s="21"/>
+      <c r="B134" s="18"/>
+      <c r="C134" s="18"/>
+      <c r="D134" s="18"/>
+      <c r="E134" s="18"/>
+      <c r="F134" s="18"/>
+      <c r="G134" s="19"/>
+      <c r="H134" s="19"/>
+    </row>
+    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A135" s="21"/>
+      <c r="B135" s="18"/>
+      <c r="C135" s="18"/>
+      <c r="D135" s="18"/>
+      <c r="E135" s="18"/>
+      <c r="F135" s="18"/>
+      <c r="G135" s="19"/>
+      <c r="H135" s="19"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1A4D219-BCFB-4495-86D8-86729423F9CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE7570E-AC27-4C12-B642-A8BC2E855C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1215" yWindow="2475" windowWidth="19200" windowHeight="10650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="696" uniqueCount="497">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="500">
   <si>
     <t>商品名称</t>
   </si>
@@ -1799,6 +1799,18 @@
   </si>
   <si>
     <t>6901028201988</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>云烟（流金印象细支）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028333269</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028333276</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2257,7 +2269,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80C0A3B-2542-45F0-B3D4-3E8698F6D850}">
-  <dimension ref="A1:K135"/>
+  <dimension ref="A1:K136"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5323,14 +5335,26 @@
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129" s="21"/>
-      <c r="B129" s="18"/>
-      <c r="C129" s="18"/>
+      <c r="A129" s="21" t="s">
+        <v>497</v>
+      </c>
+      <c r="B129" s="18">
+        <v>381.6</v>
+      </c>
+      <c r="C129" s="18">
+        <v>450</v>
+      </c>
       <c r="D129" s="18"/>
-      <c r="E129" s="18"/>
+      <c r="E129" s="18">
+        <v>45</v>
+      </c>
       <c r="F129" s="18"/>
-      <c r="G129" s="19"/>
-      <c r="H129" s="19"/>
+      <c r="G129" s="19" t="s">
+        <v>499</v>
+      </c>
+      <c r="H129" s="19" t="s">
+        <v>498</v>
+      </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="21"/>
@@ -5392,6 +5416,16 @@
       <c r="G135" s="19"/>
       <c r="H135" s="19"/>
     </row>
+    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A136" s="21"/>
+      <c r="B136" s="18"/>
+      <c r="C136" s="18"/>
+      <c r="D136" s="18"/>
+      <c r="E136" s="18"/>
+      <c r="F136" s="18"/>
+      <c r="G136" s="19"/>
+      <c r="H136" s="19"/>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FCE7570E-AC27-4C12-B642-A8BC2E855C1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614864B8-9487-43E1-9896-F287E811E1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1215" yWindow="2475" windowWidth="19200" windowHeight="10650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{614864B8-9487-43E1-9896-F287E811E1F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF246FF-D638-4220-A21C-47801B1C5AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1215" yWindow="2475" windowWidth="19200" windowHeight="10650" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="3" r:id="rId1"/>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="699" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="503">
   <si>
     <t>商品名称</t>
   </si>
@@ -1811,6 +1811,18 @@
   </si>
   <si>
     <t>6901028333276</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>娇子（宽窄锦上细支）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028268981</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028268974</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5357,14 +5369,26 @@
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" s="21"/>
-      <c r="B130" s="18"/>
-      <c r="C130" s="18"/>
+      <c r="A130" s="21" t="s">
+        <v>500</v>
+      </c>
+      <c r="B130" s="18">
+        <v>263</v>
+      </c>
+      <c r="C130" s="18">
+        <v>300</v>
+      </c>
       <c r="D130" s="18"/>
-      <c r="E130" s="18"/>
+      <c r="E130" s="18">
+        <v>30</v>
+      </c>
       <c r="F130" s="18"/>
-      <c r="G130" s="19"/>
-      <c r="H130" s="19"/>
+      <c r="G130" s="19" t="s">
+        <v>501</v>
+      </c>
+      <c r="H130" s="19" t="s">
+        <v>502</v>
+      </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="21"/>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFF246FF-D638-4220-A21C-47801B1C5AFE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD01000D-5A26-4891-A3DB-8804ACF40D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="702" uniqueCount="503">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="506">
   <si>
     <t>商品名称</t>
   </si>
@@ -1823,6 +1823,18 @@
   </si>
   <si>
     <t>6901028268974</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>牡丹（红中支）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028212250</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028212243</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5391,14 +5403,26 @@
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" s="21"/>
-      <c r="B131" s="18"/>
-      <c r="C131" s="18"/>
+      <c r="A131" s="21" t="s">
+        <v>503</v>
+      </c>
+      <c r="B131" s="18">
+        <v>175</v>
+      </c>
+      <c r="C131" s="18">
+        <v>200</v>
+      </c>
       <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
+      <c r="E131" s="18">
+        <v>20</v>
+      </c>
       <c r="F131" s="18"/>
-      <c r="G131" s="19"/>
-      <c r="H131" s="19"/>
+      <c r="G131" s="19" t="s">
+        <v>504</v>
+      </c>
+      <c r="H131" s="19" t="s">
+        <v>505</v>
+      </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A132" s="21"/>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BD01000D-5A26-4891-A3DB-8804ACF40D11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C95D63-E6FC-471D-B7D8-1CA9D4CC8618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="506">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="521">
   <si>
     <t>商品名称</t>
   </si>
@@ -1835,6 +1835,66 @@
   </si>
   <si>
     <t>6901028212243</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄金叶（天香细支）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028165365</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028165358</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>龙凤呈祥（遇见）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028228916</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028228909</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄鹤楼（冰咖）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028271004</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028939621</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>黄金叶（炫尚）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028161817</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028161800</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>玉溪（细支翡翠）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028324625</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>6901028324618</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1894,18 +1954,12 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -1923,7 +1977,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1931,41 +1985,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="3" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1977,6 +1996,40 @@
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2337,3142 +2390,3201 @@
         <v>443</v>
       </c>
     </row>
-    <row r="2" spans="1:11" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A2" s="3" t="s">
+    <row r="2" spans="1:11" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A2" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="5">
+      <c r="C2" s="8">
         <v>230</v>
       </c>
       <c r="D2" s="9">
         <v>210</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="7">
         <v>23</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="10" t="s">
         <v>320</v>
       </c>
-      <c r="H2" s="10" t="s">
+      <c r="H2" s="11" t="s">
         <v>319</v>
       </c>
-      <c r="I2" s="14"/>
-      <c r="K2" s="6"/>
-    </row>
-    <row r="3" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="6" t="s">
+      <c r="I2" s="12"/>
+      <c r="K2" s="10"/>
+    </row>
+    <row r="3" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="5">
+      <c r="C3" s="8">
         <v>150</v>
       </c>
       <c r="D3" s="9">
         <v>130</v>
       </c>
-      <c r="E3" s="4">
+      <c r="E3" s="7">
         <v>15</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="7">
         <v>15</v>
       </c>
-      <c r="G3" s="6" t="s">
+      <c r="G3" s="10" t="s">
         <v>326</v>
       </c>
-      <c r="H3" s="10" t="s">
+      <c r="H3" s="11" t="s">
         <v>327</v>
       </c>
-      <c r="I3" s="16"/>
-      <c r="K3" s="6"/>
-    </row>
-    <row r="4" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="6" t="s">
+      <c r="I3" s="14"/>
+      <c r="K3" s="10"/>
+    </row>
+    <row r="4" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="10" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" s="8" t="s">
         <v>14</v>
       </c>
       <c r="D4" s="9"/>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="7">
         <v>65</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="11" t="s">
         <v>328</v>
       </c>
-      <c r="I4" s="14"/>
-      <c r="K4" s="6"/>
-    </row>
-    <row r="5" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="6" t="s">
+      <c r="I4" s="12"/>
+      <c r="K4" s="10"/>
+    </row>
+    <row r="5" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="10" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D5" s="9"/>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="6" t="s">
+      <c r="F5" s="7"/>
+      <c r="G5" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="H5" s="10" t="s">
+      <c r="H5" s="11" t="s">
         <v>329</v>
       </c>
-      <c r="I5" s="17"/>
-      <c r="K5" s="6"/>
-    </row>
-    <row r="6" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="6" t="s">
+      <c r="I5" s="15"/>
+      <c r="K5" s="10"/>
+    </row>
+    <row r="6" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" s="8" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="4"/>
-      <c r="G6" s="6" t="s">
+      <c r="F6" s="7"/>
+      <c r="G6" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="11" t="s">
         <v>330</v>
       </c>
-      <c r="I6" s="14"/>
-      <c r="K6" s="6"/>
-    </row>
-    <row r="7" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="6" t="s">
+      <c r="I6" s="12"/>
+      <c r="K6" s="10"/>
+    </row>
+    <row r="7" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" s="8" t="s">
         <v>30</v>
       </c>
       <c r="D7" s="9"/>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="4"/>
-      <c r="G7" s="6" t="s">
+      <c r="F7" s="7"/>
+      <c r="G7" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="10" t="s">
+      <c r="H7" s="11" t="s">
         <v>331</v>
       </c>
-      <c r="I7" s="14"/>
-      <c r="K7" s="6"/>
-    </row>
-    <row r="8" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="6" t="s">
+      <c r="I7" s="12"/>
+      <c r="K7" s="10"/>
+    </row>
+    <row r="8" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="10" t="s">
         <v>33</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C8" s="5" t="s">
+      <c r="C8" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D8" s="9"/>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="6" t="s">
+      <c r="F8" s="7"/>
+      <c r="G8" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="H8" s="10" t="s">
+      <c r="H8" s="11" t="s">
         <v>332</v>
       </c>
-      <c r="I8" s="14"/>
-      <c r="K8" s="6"/>
-    </row>
-    <row r="9" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="6" t="s">
+      <c r="I8" s="12"/>
+      <c r="K8" s="10"/>
+    </row>
+    <row r="9" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="5" t="s">
+      <c r="C9" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D9" s="9"/>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="6" t="s">
+      <c r="F9" s="7"/>
+      <c r="G9" s="10" t="s">
         <v>314</v>
       </c>
-      <c r="H9" s="10" t="s">
+      <c r="H9" s="11" t="s">
         <v>333</v>
       </c>
-      <c r="I9" s="14"/>
-      <c r="K9" s="6"/>
-    </row>
-    <row r="10" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="6" t="s">
+      <c r="I9" s="12"/>
+      <c r="K9" s="10"/>
+    </row>
+    <row r="10" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C10" s="5" t="s">
+      <c r="C10" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D10" s="9"/>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="6" t="s">
+      <c r="F10" s="7"/>
+      <c r="G10" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="H10" s="10" t="s">
+      <c r="H10" s="11" t="s">
         <v>334</v>
       </c>
-      <c r="I10" s="14"/>
-      <c r="K10" s="6"/>
-    </row>
-    <row r="11" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="6" t="s">
+      <c r="I10" s="12"/>
+      <c r="K10" s="10"/>
+    </row>
+    <row r="11" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="7" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="8" t="s">
         <v>21</v>
       </c>
       <c r="D11" s="9"/>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="7" t="s">
         <v>47</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="6" t="s">
+      <c r="F11" s="7"/>
+      <c r="G11" s="10" t="s">
         <v>44</v>
       </c>
-      <c r="H11" s="10" t="s">
+      <c r="H11" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="I11" s="14"/>
-      <c r="K11" s="6"/>
-    </row>
-    <row r="12" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="6" t="s">
+      <c r="I11" s="12"/>
+      <c r="K11" s="10"/>
+    </row>
+    <row r="12" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B12" s="4">
+      <c r="B12" s="7">
         <v>201.4</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D12" s="9"/>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="6" t="s">
+      <c r="F12" s="7"/>
+      <c r="G12" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="10" t="s">
+      <c r="H12" s="11" t="s">
         <v>336</v>
       </c>
-      <c r="I12" s="14"/>
-      <c r="K12" s="6"/>
-    </row>
-    <row r="13" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="6" t="s">
+      <c r="I12" s="12"/>
+      <c r="K12" s="10"/>
+    </row>
+    <row r="13" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="10" t="s">
         <v>52</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D13" s="9">
         <v>360</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="6" t="s">
+      <c r="F13" s="7"/>
+      <c r="G13" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="10" t="s">
+      <c r="H13" s="11" t="s">
         <v>337</v>
       </c>
-      <c r="I13" s="14"/>
-      <c r="K13" s="6"/>
-    </row>
-    <row r="14" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="6" t="s">
+      <c r="I13" s="12"/>
+      <c r="K13" s="10"/>
+    </row>
+    <row r="14" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="7" t="s">
         <v>58</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D14" s="9">
         <v>107</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="6" t="s">
+      <c r="F14" s="7"/>
+      <c r="G14" s="10" t="s">
         <v>56</v>
       </c>
-      <c r="H14" s="10" t="s">
+      <c r="H14" s="11" t="s">
         <v>338</v>
       </c>
-      <c r="I14" s="14"/>
-      <c r="K14" s="6"/>
-    </row>
-    <row r="15" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="6" t="s">
+      <c r="I14" s="12"/>
+      <c r="K14" s="10"/>
+    </row>
+    <row r="15" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="10" t="s">
         <v>62</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="8" t="s">
         <v>64</v>
       </c>
       <c r="D15" s="9"/>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="7" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="6" t="s">
+      <c r="F15" s="7"/>
+      <c r="G15" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="H15" s="10" t="s">
+      <c r="H15" s="11" t="s">
         <v>339</v>
       </c>
-      <c r="I15" s="14"/>
-      <c r="K15" s="6"/>
-    </row>
-    <row r="16" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A16" s="6" t="s">
+      <c r="I15" s="12"/>
+      <c r="K15" s="10"/>
+    </row>
+    <row r="16" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="10" t="s">
         <v>67</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="5" t="s">
+      <c r="C16" s="8" t="s">
         <v>69</v>
       </c>
       <c r="D16" s="9">
         <v>107</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="F16" s="4"/>
-      <c r="G16" s="6" t="s">
+      <c r="F16" s="7"/>
+      <c r="G16" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="H16" s="10" t="s">
+      <c r="H16" s="11" t="s">
         <v>340</v>
       </c>
-      <c r="I16" s="14"/>
-      <c r="K16" s="6"/>
-    </row>
-    <row r="17" spans="1:11" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A17" s="3" t="s">
+      <c r="I16" s="12"/>
+      <c r="K16" s="10"/>
+    </row>
+    <row r="17" spans="1:11" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A17" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C17" s="5" t="s">
+      <c r="C17" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D17" s="9"/>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="6" t="s">
+      <c r="F17" s="7"/>
+      <c r="G17" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="H17" s="10" t="s">
+      <c r="H17" s="11" t="s">
         <v>342</v>
       </c>
-      <c r="I17" s="14"/>
-      <c r="K17" s="6"/>
-    </row>
-    <row r="18" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A18" s="6" t="s">
+      <c r="I17" s="12"/>
+      <c r="K17" s="10"/>
+    </row>
+    <row r="18" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="10" t="s">
         <v>76</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C18" s="5" t="s">
+      <c r="C18" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D18" s="9"/>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F18" s="4"/>
-      <c r="G18" s="6" t="s">
+      <c r="F18" s="7"/>
+      <c r="G18" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="H18" s="10" t="s">
+      <c r="H18" s="11" t="s">
         <v>343</v>
       </c>
-      <c r="I18" s="14"/>
-      <c r="K18" s="6"/>
-    </row>
-    <row r="19" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A19" s="6" t="s">
+      <c r="I18" s="12"/>
+      <c r="K18" s="10"/>
+    </row>
+    <row r="19" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="7" t="s">
         <v>80</v>
       </c>
-      <c r="C19" s="5" t="s">
+      <c r="C19" s="8" t="s">
         <v>40</v>
       </c>
       <c r="D19" s="9"/>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="7" t="s">
         <v>34</v>
       </c>
-      <c r="F19" s="4"/>
-      <c r="G19" s="6" t="s">
+      <c r="F19" s="7"/>
+      <c r="G19" s="10" t="s">
         <v>78</v>
       </c>
-      <c r="H19" s="10" t="s">
+      <c r="H19" s="11" t="s">
         <v>344</v>
       </c>
-      <c r="I19" s="14"/>
-      <c r="K19" s="6"/>
-    </row>
-    <row r="20" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A20" s="6" t="s">
+      <c r="I19" s="12"/>
+      <c r="K19" s="10"/>
+    </row>
+    <row r="20" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C20" s="5" t="s">
+      <c r="C20" s="8" t="s">
         <v>82</v>
       </c>
       <c r="D20" s="9"/>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F20" s="4"/>
-      <c r="G20" s="6" t="s">
+      <c r="F20" s="7"/>
+      <c r="G20" s="10" t="s">
         <v>345</v>
       </c>
-      <c r="H20" s="10" t="s">
+      <c r="H20" s="11" t="s">
         <v>317</v>
       </c>
-      <c r="I20" s="14"/>
-      <c r="K20" s="6"/>
-    </row>
-    <row r="21" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A21" s="6" t="s">
+      <c r="I20" s="12"/>
+      <c r="K20" s="10"/>
+    </row>
+    <row r="21" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="10" t="s">
         <v>84</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C21" s="5" t="s">
+      <c r="C21" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D21" s="9"/>
-      <c r="E21" s="4" t="s">
+      <c r="E21" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F21" s="4"/>
-      <c r="G21" s="6" t="s">
+      <c r="F21" s="7"/>
+      <c r="G21" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="H21" s="10" t="s">
+      <c r="H21" s="11" t="s">
         <v>346</v>
       </c>
-      <c r="I21" s="14"/>
-      <c r="K21" s="6"/>
-    </row>
-    <row r="22" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A22" s="6" t="s">
+      <c r="I21" s="12"/>
+      <c r="K21" s="10"/>
+    </row>
+    <row r="22" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="7" t="s">
         <v>89</v>
       </c>
-      <c r="C22" s="5" t="s">
+      <c r="C22" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D22" s="9"/>
-      <c r="E22" s="4">
+      <c r="E22" s="7">
         <v>13</v>
       </c>
-      <c r="F22" s="4"/>
-      <c r="G22" s="6" t="s">
+      <c r="F22" s="7"/>
+      <c r="G22" s="10" t="s">
         <v>441</v>
       </c>
-      <c r="H22" s="10" t="s">
+      <c r="H22" s="11" t="s">
         <v>442</v>
       </c>
-      <c r="I22" s="14"/>
-      <c r="K22" s="6"/>
-    </row>
-    <row r="23" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A23" s="6" t="s">
+      <c r="I22" s="12"/>
+      <c r="K22" s="10"/>
+    </row>
+    <row r="23" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C23" s="5" t="s">
+      <c r="C23" s="8" t="s">
         <v>20</v>
       </c>
       <c r="D23" s="9"/>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="7" t="s">
         <v>21</v>
       </c>
-      <c r="F23" s="4"/>
-      <c r="G23" s="6" t="s">
+      <c r="F23" s="7"/>
+      <c r="G23" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="H23" s="10" t="s">
+      <c r="H23" s="11" t="s">
         <v>347</v>
       </c>
-      <c r="I23" s="14"/>
-      <c r="K23" s="6"/>
-    </row>
-    <row r="24" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="6" t="s">
+      <c r="I23" s="12"/>
+      <c r="K23" s="10"/>
+    </row>
+    <row r="24" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="B24" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C24" s="5" t="s">
+      <c r="C24" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D24" s="9"/>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F24" s="4"/>
-      <c r="G24" s="6" t="s">
+      <c r="F24" s="7"/>
+      <c r="G24" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="H24" s="10" t="s">
+      <c r="H24" s="11" t="s">
         <v>348</v>
       </c>
-      <c r="I24" s="14"/>
-      <c r="K24" s="6"/>
-    </row>
-    <row r="25" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="6" t="s">
+      <c r="I24" s="12"/>
+      <c r="K24" s="10"/>
+    </row>
+    <row r="25" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="B25" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C25" s="5" t="s">
+      <c r="C25" s="8" t="s">
         <v>97</v>
       </c>
       <c r="D25" s="9"/>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F25" s="4"/>
-      <c r="G25" s="6" t="s">
+      <c r="F25" s="7"/>
+      <c r="G25" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H25" s="10" t="s">
+      <c r="H25" s="11" t="s">
         <v>349</v>
       </c>
-      <c r="I25" s="14"/>
-      <c r="K25" s="6"/>
-    </row>
-    <row r="26" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A26" s="6" t="s">
+      <c r="I25" s="12"/>
+      <c r="K25" s="10"/>
+    </row>
+    <row r="26" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="10" t="s">
         <v>100</v>
       </c>
-      <c r="B26" s="4" t="s">
+      <c r="B26" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C26" s="5" t="s">
+      <c r="C26" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D26" s="9"/>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="4"/>
-      <c r="G26" s="6" t="s">
+      <c r="F26" s="7"/>
+      <c r="G26" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="H26" s="10" t="s">
+      <c r="H26" s="11" t="s">
         <v>364</v>
       </c>
-      <c r="I26" s="14"/>
-      <c r="K26" s="6"/>
-    </row>
-    <row r="27" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="6" t="s">
+      <c r="I26" s="12"/>
+      <c r="K26" s="10"/>
+    </row>
+    <row r="27" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A27" s="10" t="s">
         <v>103</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="B27" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C27" s="5" t="s">
+      <c r="C27" s="8" t="s">
         <v>105</v>
       </c>
       <c r="D27" s="9"/>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F27" s="4"/>
-      <c r="G27" s="6" t="s">
+      <c r="F27" s="7"/>
+      <c r="G27" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="H27" s="10"/>
-      <c r="I27" s="14"/>
-      <c r="K27" s="6"/>
-    </row>
-    <row r="28" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
+      <c r="H27" s="11"/>
+      <c r="I27" s="12"/>
+      <c r="K27" s="10"/>
+    </row>
+    <row r="28" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="B28" s="4" t="s">
+      <c r="B28" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C28" s="5" t="s">
+      <c r="C28" s="8" t="s">
         <v>105</v>
       </c>
       <c r="D28" s="9"/>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F28" s="4"/>
-      <c r="G28" s="6" t="s">
+      <c r="F28" s="7"/>
+      <c r="G28" s="10" t="s">
         <v>108</v>
       </c>
-      <c r="H28" s="10" t="s">
+      <c r="H28" s="11" t="s">
         <v>350</v>
       </c>
-      <c r="I28" s="14"/>
-      <c r="K28" s="6"/>
-    </row>
-    <row r="29" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A29" s="6" t="s">
+      <c r="I28" s="12"/>
+      <c r="K28" s="10"/>
+    </row>
+    <row r="29" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A29" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="4" t="s">
+      <c r="B29" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C29" s="5" t="s">
+      <c r="C29" s="8" t="s">
         <v>105</v>
       </c>
       <c r="D29" s="9"/>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F29" s="4"/>
-      <c r="G29" s="6" t="s">
+      <c r="F29" s="7"/>
+      <c r="G29" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="H29" s="10" t="s">
+      <c r="H29" s="11" t="s">
         <v>351</v>
       </c>
-      <c r="I29" s="14"/>
-      <c r="K29" s="6"/>
-    </row>
-    <row r="30" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="6" t="s">
+      <c r="I29" s="12"/>
+      <c r="K29" s="10"/>
+    </row>
+    <row r="30" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A30" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="B30" s="4" t="s">
+      <c r="B30" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C30" s="5" t="s">
+      <c r="C30" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D30" s="9"/>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F30" s="4"/>
-      <c r="G30" s="6" t="s">
+      <c r="F30" s="7"/>
+      <c r="G30" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="H30" s="10" t="s">
+      <c r="H30" s="11" t="s">
         <v>352</v>
       </c>
-      <c r="I30" s="14"/>
-      <c r="K30" s="6"/>
-    </row>
-    <row r="31" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A31" s="6" t="s">
+      <c r="I30" s="12"/>
+      <c r="K30" s="10"/>
+    </row>
+    <row r="31" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="B31" s="4" t="s">
+      <c r="B31" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C31" s="5" t="s">
+      <c r="C31" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D31" s="9"/>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F31" s="4"/>
-      <c r="G31" s="6" t="s">
+      <c r="F31" s="7"/>
+      <c r="G31" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="H31" s="10" t="s">
+      <c r="H31" s="11" t="s">
         <v>353</v>
       </c>
-      <c r="I31" s="14"/>
-      <c r="K31" s="6"/>
-    </row>
-    <row r="32" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A32" s="6" t="s">
+      <c r="I31" s="12"/>
+      <c r="K31" s="10"/>
+    </row>
+    <row r="32" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A32" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="B32" s="4" t="s">
+      <c r="B32" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C32" s="5" t="s">
+      <c r="C32" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D32" s="9">
         <v>160</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F32" s="4"/>
-      <c r="G32" s="6" t="s">
+      <c r="F32" s="7"/>
+      <c r="G32" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="H32" s="10" t="s">
+      <c r="H32" s="11" t="s">
         <v>354</v>
       </c>
-      <c r="I32" s="14"/>
-      <c r="K32" s="6"/>
-    </row>
-    <row r="33" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="6" t="s">
+      <c r="I32" s="12"/>
+      <c r="K32" s="10"/>
+    </row>
+    <row r="33" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A33" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="B33" s="4" t="s">
+      <c r="B33" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C33" s="5" t="s">
+      <c r="C33" s="8" t="s">
         <v>122</v>
       </c>
       <c r="D33" s="9"/>
-      <c r="E33" s="4" t="s">
+      <c r="E33" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F33" s="4"/>
-      <c r="G33" s="6" t="s">
+      <c r="F33" s="7"/>
+      <c r="G33" s="10" t="s">
         <v>119</v>
       </c>
-      <c r="H33" s="10" t="s">
+      <c r="H33" s="11" t="s">
         <v>355</v>
       </c>
-      <c r="I33" s="14"/>
-      <c r="K33" s="6"/>
-    </row>
-    <row r="34" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="6" t="s">
+      <c r="I33" s="12"/>
+      <c r="K33" s="10"/>
+    </row>
+    <row r="34" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A34" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="B34" s="4" t="s">
+      <c r="B34" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C34" s="5" t="s">
+      <c r="C34" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D34" s="9"/>
-      <c r="E34" s="4" t="s">
+      <c r="E34" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F34" s="4"/>
-      <c r="G34" s="6" t="s">
+      <c r="F34" s="7"/>
+      <c r="G34" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="H34" s="10" t="s">
+      <c r="H34" s="11" t="s">
         <v>356</v>
       </c>
-      <c r="I34" s="14"/>
-      <c r="K34" s="6"/>
-    </row>
-    <row r="35" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="6" t="s">
+      <c r="I34" s="12"/>
+      <c r="K34" s="10"/>
+    </row>
+    <row r="35" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A35" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="B35" s="4" t="s">
+      <c r="B35" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C35" s="5" t="s">
+      <c r="C35" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D35" s="9"/>
-      <c r="E35" s="4" t="s">
+      <c r="E35" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F35" s="4"/>
-      <c r="G35" s="6" t="s">
+      <c r="F35" s="7"/>
+      <c r="G35" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="H35" s="10" t="s">
+      <c r="H35" s="11" t="s">
         <v>357</v>
       </c>
-      <c r="I35" s="14"/>
-      <c r="K35" s="6"/>
-    </row>
-    <row r="36" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="6" t="s">
+      <c r="I35" s="12"/>
+      <c r="K35" s="10"/>
+    </row>
+    <row r="36" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A36" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="B36" s="4" t="s">
+      <c r="B36" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C36" s="5" t="s">
+      <c r="C36" s="8" t="s">
         <v>97</v>
       </c>
       <c r="D36" s="9"/>
-      <c r="E36" s="4" t="s">
+      <c r="E36" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F36" s="4"/>
-      <c r="G36" s="6" t="s">
+      <c r="F36" s="7"/>
+      <c r="G36" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="H36" s="10" t="s">
+      <c r="H36" s="11" t="s">
         <v>358</v>
       </c>
-      <c r="I36" s="14"/>
-      <c r="K36" s="6"/>
-    </row>
-    <row r="37" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A37" s="6" t="s">
+      <c r="I36" s="12"/>
+      <c r="K36" s="10"/>
+    </row>
+    <row r="37" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A37" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="B37" s="4" t="s">
+      <c r="B37" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C37" s="5" t="s">
+      <c r="C37" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D37" s="9"/>
-      <c r="E37" s="4" t="s">
+      <c r="E37" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F37" s="4"/>
-      <c r="G37" s="6" t="s">
+      <c r="F37" s="7"/>
+      <c r="G37" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="H37" s="10" t="s">
+      <c r="H37" s="11" t="s">
         <v>359</v>
       </c>
-      <c r="I37" s="14"/>
-      <c r="K37" s="6"/>
-    </row>
-    <row r="38" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A38" s="6" t="s">
+      <c r="I37" s="12"/>
+      <c r="K37" s="10"/>
+    </row>
+    <row r="38" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A38" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="B38" s="4" t="s">
+      <c r="B38" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C38" s="5" t="s">
+      <c r="C38" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D38" s="9"/>
-      <c r="E38" s="4" t="s">
+      <c r="E38" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F38" s="4"/>
-      <c r="G38" s="6" t="s">
+      <c r="F38" s="7"/>
+      <c r="G38" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="H38" s="10" t="s">
+      <c r="H38" s="11" t="s">
         <v>360</v>
       </c>
-      <c r="I38" s="14"/>
-      <c r="K38" s="6"/>
-    </row>
-    <row r="39" spans="1:11" s="7" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
-      <c r="A39" s="8" t="s">
+      <c r="I38" s="12"/>
+      <c r="K38" s="10"/>
+    </row>
+    <row r="39" spans="1:11" s="13" customFormat="1" ht="16.5" x14ac:dyDescent="0.2">
+      <c r="A39" s="16" t="s">
         <v>321</v>
       </c>
-      <c r="B39" s="4">
+      <c r="B39" s="7">
         <v>155</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C39" s="8">
         <v>180</v>
       </c>
       <c r="D39" s="9">
         <v>170</v>
       </c>
-      <c r="E39" s="4">
+      <c r="E39" s="7">
         <v>18</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="7">
         <v>18</v>
       </c>
-      <c r="G39" s="6" t="s">
+      <c r="G39" s="10" t="s">
         <v>322</v>
       </c>
-      <c r="H39" s="10" t="s">
+      <c r="H39" s="11" t="s">
         <v>325</v>
       </c>
-      <c r="I39" s="14"/>
-      <c r="K39" s="6"/>
-    </row>
-    <row r="40" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A40" s="6" t="s">
+      <c r="I39" s="12"/>
+      <c r="K39" s="10"/>
+    </row>
+    <row r="40" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A40" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="B40" s="4" t="s">
+      <c r="B40" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C40" s="5" t="s">
+      <c r="C40" s="8" t="s">
         <v>105</v>
       </c>
       <c r="D40" s="9"/>
-      <c r="E40" s="4" t="s">
+      <c r="E40" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F40" s="4"/>
-      <c r="G40" s="6" t="s">
+      <c r="F40" s="7"/>
+      <c r="G40" s="10" t="s">
         <v>133</v>
       </c>
-      <c r="H40" s="10" t="s">
+      <c r="H40" s="11" t="s">
         <v>361</v>
       </c>
-      <c r="I40" s="14"/>
-      <c r="K40" s="6"/>
-    </row>
-    <row r="41" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A41" s="6" t="s">
+      <c r="I40" s="12"/>
+      <c r="K40" s="10"/>
+    </row>
+    <row r="41" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A41" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="B41" s="4" t="s">
+      <c r="B41" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C41" s="5" t="s">
+      <c r="C41" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D41" s="9"/>
-      <c r="E41" s="4" t="s">
+      <c r="E41" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F41" s="4"/>
-      <c r="G41" s="6" t="s">
+      <c r="F41" s="7"/>
+      <c r="G41" s="10" t="s">
         <v>135</v>
       </c>
-      <c r="H41" s="10" t="s">
+      <c r="H41" s="11" t="s">
         <v>362</v>
       </c>
-      <c r="I41" s="14"/>
-      <c r="K41" s="6"/>
-    </row>
-    <row r="42" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A42" s="6" t="s">
+      <c r="I41" s="12"/>
+      <c r="K41" s="10"/>
+    </row>
+    <row r="42" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A42" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="B42" s="4" t="s">
+      <c r="B42" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C42" s="5" t="s">
+      <c r="C42" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D42" s="9"/>
-      <c r="E42" s="4" t="s">
+      <c r="E42" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F42" s="4"/>
-      <c r="G42" s="6" t="s">
+      <c r="F42" s="7"/>
+      <c r="G42" s="10" t="s">
         <v>137</v>
       </c>
-      <c r="H42" s="10" t="s">
+      <c r="H42" s="11" t="s">
         <v>363</v>
       </c>
-      <c r="I42" s="14"/>
-      <c r="K42" s="6"/>
-    </row>
-    <row r="43" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="6" t="s">
+      <c r="I42" s="12"/>
+      <c r="K42" s="10"/>
+    </row>
+    <row r="43" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A43" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="B43" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C43" s="5" t="s">
+      <c r="C43" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D43" s="9"/>
-      <c r="E43" s="4" t="s">
+      <c r="E43" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F43" s="4"/>
-      <c r="G43" s="6" t="s">
+      <c r="F43" s="7"/>
+      <c r="G43" s="10" t="s">
         <v>139</v>
       </c>
-      <c r="H43" s="10" t="s">
+      <c r="H43" s="11" t="s">
         <v>365</v>
       </c>
-      <c r="I43" s="14"/>
-      <c r="K43" s="6"/>
-    </row>
-    <row r="44" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A44" s="6" t="s">
+      <c r="I43" s="12"/>
+      <c r="K43" s="10"/>
+    </row>
+    <row r="44" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A44" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="B44" s="4" t="s">
+      <c r="B44" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C44" s="5" t="s">
+      <c r="C44" s="8" t="s">
         <v>97</v>
       </c>
       <c r="D44" s="9"/>
-      <c r="E44" s="4" t="s">
+      <c r="E44" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F44" s="4"/>
-      <c r="G44" s="6" t="s">
+      <c r="F44" s="7"/>
+      <c r="G44" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="H44" s="10" t="s">
+      <c r="H44" s="11" t="s">
         <v>366</v>
       </c>
-      <c r="I44" s="14"/>
-      <c r="K44" s="6"/>
-    </row>
-    <row r="45" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A45" s="6" t="s">
+      <c r="I44" s="12"/>
+      <c r="K44" s="10"/>
+    </row>
+    <row r="45" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A45" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="B45" s="4" t="s">
+      <c r="B45" s="7" t="s">
         <v>141</v>
       </c>
-      <c r="C45" s="5" t="s">
+      <c r="C45" s="8" t="s">
         <v>82</v>
       </c>
       <c r="D45" s="9">
         <v>120</v>
       </c>
-      <c r="E45" s="4" t="s">
+      <c r="E45" s="7" t="s">
         <v>18</v>
       </c>
-      <c r="F45" s="4"/>
-      <c r="G45" s="6" t="s">
+      <c r="F45" s="7"/>
+      <c r="G45" s="10" t="s">
         <v>144</v>
       </c>
-      <c r="H45" s="10" t="s">
+      <c r="H45" s="11" t="s">
         <v>367</v>
       </c>
-      <c r="I45" s="14"/>
-      <c r="K45" s="6"/>
-    </row>
-    <row r="46" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A46" s="6" t="s">
+      <c r="I45" s="12"/>
+      <c r="K45" s="10"/>
+    </row>
+    <row r="46" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A46" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="B46" s="4" t="s">
+      <c r="B46" s="7" t="s">
         <v>148</v>
       </c>
-      <c r="C46" s="5" t="s">
+      <c r="C46" s="8" t="s">
         <v>30</v>
       </c>
       <c r="D46" s="9"/>
-      <c r="E46" s="4" t="s">
+      <c r="E46" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="F46" s="4"/>
-      <c r="G46" s="6" t="s">
+      <c r="F46" s="7"/>
+      <c r="G46" s="10" t="s">
         <v>146</v>
       </c>
-      <c r="H46" s="10" t="s">
+      <c r="H46" s="11" t="s">
         <v>368</v>
       </c>
-      <c r="I46" s="14"/>
-      <c r="K46" s="6"/>
-    </row>
-    <row r="47" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A47" s="6" t="s">
+      <c r="I46" s="12"/>
+      <c r="K46" s="10"/>
+    </row>
+    <row r="47" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A47" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="B47" s="4" t="s">
+      <c r="B47" s="7" t="s">
         <v>152</v>
       </c>
-      <c r="C47" s="5" t="s">
+      <c r="C47" s="8" t="s">
         <v>153</v>
       </c>
       <c r="D47" s="9"/>
-      <c r="E47" s="4" t="s">
+      <c r="E47" s="7" t="s">
         <v>154</v>
       </c>
-      <c r="F47" s="4"/>
-      <c r="G47" s="6" t="s">
+      <c r="F47" s="7"/>
+      <c r="G47" s="10" t="s">
         <v>149</v>
       </c>
-      <c r="H47" s="10" t="s">
+      <c r="H47" s="11" t="s">
         <v>369</v>
       </c>
-      <c r="I47" s="14"/>
-      <c r="K47" s="6"/>
-    </row>
-    <row r="48" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A48" s="6" t="s">
+      <c r="I47" s="12"/>
+      <c r="K47" s="10"/>
+    </row>
+    <row r="48" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A48" s="10" t="s">
         <v>156</v>
       </c>
-      <c r="B48" s="4" t="s">
+      <c r="B48" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="C48" s="5" t="s">
+      <c r="C48" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D48" s="9"/>
-      <c r="E48" s="4" t="s">
+      <c r="E48" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="F48" s="4"/>
-      <c r="G48" s="6" t="s">
+      <c r="F48" s="7"/>
+      <c r="G48" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="H48" s="10" t="s">
+      <c r="H48" s="11" t="s">
         <v>370</v>
       </c>
-      <c r="I48" s="14"/>
-      <c r="K48" s="6"/>
-    </row>
-    <row r="49" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A49" s="6" t="s">
+      <c r="I48" s="12"/>
+      <c r="K48" s="10"/>
+    </row>
+    <row r="49" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A49" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="B49" s="4" t="s">
+      <c r="B49" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C49" s="5" t="s">
+      <c r="C49" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D49" s="9"/>
-      <c r="E49" s="4" t="s">
+      <c r="E49" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F49" s="4"/>
-      <c r="G49" s="6" t="s">
+      <c r="F49" s="7"/>
+      <c r="G49" s="10" t="s">
         <v>159</v>
       </c>
-      <c r="H49" s="10" t="s">
+      <c r="H49" s="11" t="s">
         <v>371</v>
       </c>
-      <c r="I49" s="14"/>
-      <c r="K49" s="6"/>
-    </row>
-    <row r="50" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A50" s="6" t="s">
+      <c r="I49" s="12"/>
+      <c r="K49" s="10"/>
+    </row>
+    <row r="50" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A50" s="10" t="s">
         <v>163</v>
       </c>
-      <c r="B50" s="4" t="s">
+      <c r="B50" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D50" s="9"/>
-      <c r="E50" s="4" t="s">
+      <c r="E50" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F50" s="4"/>
-      <c r="G50" s="6" t="s">
+      <c r="F50" s="7"/>
+      <c r="G50" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="H50" s="11" t="s">
+      <c r="H50" s="17" t="s">
         <v>372</v>
       </c>
-      <c r="I50" s="14"/>
-      <c r="K50" s="6"/>
-    </row>
-    <row r="51" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A51" s="6" t="s">
+      <c r="I50" s="12"/>
+      <c r="K50" s="10"/>
+    </row>
+    <row r="51" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A51" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="B51" s="4" t="s">
+      <c r="B51" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="8" t="s">
         <v>122</v>
       </c>
       <c r="D51" s="9"/>
-      <c r="E51" s="4" t="s">
+      <c r="E51" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F51" s="4"/>
-      <c r="G51" s="6" t="s">
+      <c r="F51" s="7"/>
+      <c r="G51" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="H51" s="11" t="s">
+      <c r="H51" s="17" t="s">
         <v>373</v>
       </c>
-      <c r="I51" s="14"/>
-      <c r="K51" s="6"/>
-    </row>
-    <row r="52" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A52" s="6" t="s">
+      <c r="I51" s="12"/>
+      <c r="K51" s="10"/>
+    </row>
+    <row r="52" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A52" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="B52" s="4" t="s">
+      <c r="B52" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D52" s="9"/>
-      <c r="E52" s="4" t="s">
+      <c r="E52" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F52" s="4"/>
-      <c r="G52" s="6" t="s">
+      <c r="F52" s="7"/>
+      <c r="G52" s="10" t="s">
         <v>166</v>
       </c>
-      <c r="H52" s="11" t="s">
+      <c r="H52" s="17" t="s">
         <v>374</v>
       </c>
-      <c r="I52" s="14"/>
-      <c r="K52" s="6"/>
-    </row>
-    <row r="53" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A53" s="6" t="s">
+      <c r="I52" s="12"/>
+      <c r="K52" s="10"/>
+    </row>
+    <row r="53" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A53" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="B53" s="4" t="s">
+      <c r="B53" s="7" t="s">
         <v>170</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="8" t="s">
         <v>171</v>
       </c>
       <c r="D53" s="9"/>
-      <c r="E53" s="4" t="s">
+      <c r="E53" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F53" s="4"/>
-      <c r="G53" s="6" t="s">
+      <c r="F53" s="7"/>
+      <c r="G53" s="10" t="s">
         <v>168</v>
       </c>
-      <c r="H53" s="11" t="s">
+      <c r="H53" s="17" t="s">
         <v>375</v>
       </c>
-      <c r="I53" s="14"/>
-      <c r="K53" s="6"/>
-    </row>
-    <row r="54" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A54" s="6" t="s">
+      <c r="I53" s="12"/>
+      <c r="K53" s="10"/>
+    </row>
+    <row r="54" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A54" s="10" t="s">
         <v>174</v>
       </c>
-      <c r="B54" s="4" t="s">
+      <c r="B54" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D54" s="9"/>
-      <c r="E54" s="4" t="s">
+      <c r="E54" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F54" s="4"/>
-      <c r="G54" s="6" t="s">
+      <c r="F54" s="7"/>
+      <c r="G54" s="10" t="s">
         <v>173</v>
       </c>
-      <c r="H54" s="11" t="s">
+      <c r="H54" s="17" t="s">
         <v>376</v>
       </c>
-      <c r="I54" s="14"/>
-      <c r="K54" s="6"/>
-    </row>
-    <row r="55" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A55" s="6" t="s">
+      <c r="I54" s="12"/>
+      <c r="K54" s="10"/>
+    </row>
+    <row r="55" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A55" s="10" t="s">
         <v>176</v>
       </c>
-      <c r="B55" s="4" t="s">
+      <c r="B55" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D55" s="9"/>
-      <c r="E55" s="4" t="s">
+      <c r="E55" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F55" s="4"/>
-      <c r="G55" s="6" t="s">
+      <c r="F55" s="7"/>
+      <c r="G55" s="10" t="s">
         <v>175</v>
       </c>
-      <c r="H55" s="11" t="s">
+      <c r="H55" s="17" t="s">
         <v>377</v>
       </c>
-      <c r="I55" s="14"/>
-      <c r="K55" s="6"/>
-    </row>
-    <row r="56" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A56" s="6" t="s">
+      <c r="I55" s="12"/>
+      <c r="K55" s="10"/>
+    </row>
+    <row r="56" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A56" s="10" t="s">
         <v>178</v>
       </c>
-      <c r="B56" s="4" t="s">
+      <c r="B56" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="8" t="s">
         <v>105</v>
       </c>
       <c r="D56" s="9"/>
-      <c r="E56" s="4" t="s">
+      <c r="E56" s="7" t="s">
         <v>106</v>
       </c>
-      <c r="F56" s="4"/>
-      <c r="G56" s="6" t="s">
+      <c r="F56" s="7"/>
+      <c r="G56" s="10" t="s">
         <v>177</v>
       </c>
-      <c r="H56" s="11" t="s">
+      <c r="H56" s="17" t="s">
         <v>378</v>
       </c>
-      <c r="I56" s="14"/>
-      <c r="K56" s="6"/>
-    </row>
-    <row r="57" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A57" s="6" t="s">
+      <c r="I56" s="12"/>
+      <c r="K56" s="10"/>
+    </row>
+    <row r="57" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A57" s="10" t="s">
         <v>180</v>
       </c>
-      <c r="B57" s="4" t="s">
+      <c r="B57" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="8" t="s">
         <v>181</v>
       </c>
       <c r="D57" s="9"/>
-      <c r="E57" s="4" t="s">
+      <c r="E57" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F57" s="4"/>
-      <c r="G57" s="6" t="s">
+      <c r="F57" s="7"/>
+      <c r="G57" s="10" t="s">
         <v>179</v>
       </c>
-      <c r="H57" s="11" t="s">
+      <c r="H57" s="17" t="s">
         <v>379</v>
       </c>
-      <c r="I57" s="14"/>
-      <c r="K57" s="6"/>
-    </row>
-    <row r="58" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A58" s="6" t="s">
+      <c r="I57" s="12"/>
+      <c r="K57" s="10"/>
+    </row>
+    <row r="58" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A58" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B58" s="4" t="s">
+      <c r="B58" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D58" s="9"/>
-      <c r="E58" s="4" t="s">
+      <c r="E58" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F58" s="4"/>
-      <c r="G58" s="6" t="s">
+      <c r="F58" s="7"/>
+      <c r="G58" s="10" t="s">
         <v>184</v>
       </c>
-      <c r="H58" s="11" t="s">
+      <c r="H58" s="17" t="s">
         <v>380</v>
       </c>
-      <c r="I58" s="14"/>
-      <c r="K58" s="6"/>
-    </row>
-    <row r="59" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A59" s="6" t="s">
+      <c r="I58" s="12"/>
+      <c r="K58" s="10"/>
+    </row>
+    <row r="59" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A59" s="10" t="s">
         <v>187</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="B59" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="8" t="s">
         <v>5</v>
       </c>
       <c r="D59" s="9"/>
-      <c r="E59" s="4" t="s">
+      <c r="E59" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="F59" s="4"/>
-      <c r="G59" s="6" t="s">
+      <c r="F59" s="7"/>
+      <c r="G59" s="10" t="s">
         <v>186</v>
       </c>
-      <c r="H59" s="11" t="s">
+      <c r="H59" s="17" t="s">
         <v>381</v>
       </c>
-      <c r="I59" s="14"/>
-      <c r="K59" s="6"/>
-    </row>
-    <row r="60" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A60" s="6" t="s">
+      <c r="I59" s="12"/>
+      <c r="K59" s="10"/>
+    </row>
+    <row r="60" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A60" s="10" t="s">
         <v>189</v>
       </c>
-      <c r="B60" s="4" t="s">
+      <c r="B60" s="7" t="s">
         <v>77</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="8" t="s">
         <v>97</v>
       </c>
       <c r="D60" s="9"/>
-      <c r="E60" s="4" t="s">
+      <c r="E60" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="F60" s="4"/>
-      <c r="G60" s="6" t="s">
+      <c r="F60" s="7"/>
+      <c r="G60" s="10" t="s">
         <v>188</v>
       </c>
-      <c r="H60" s="11" t="s">
+      <c r="H60" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="I60" s="14"/>
-      <c r="K60" s="6"/>
-    </row>
-    <row r="61" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A61" s="6" t="s">
+      <c r="I60" s="12"/>
+      <c r="K60" s="10"/>
+    </row>
+    <row r="61" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A61" s="10" t="s">
         <v>191</v>
       </c>
-      <c r="B61" s="4" t="s">
+      <c r="B61" s="7" t="s">
         <v>192</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="8" t="s">
         <v>122</v>
       </c>
       <c r="D61" s="9"/>
-      <c r="E61" s="4" t="s">
+      <c r="E61" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F61" s="4"/>
-      <c r="G61" s="6" t="s">
+      <c r="F61" s="7"/>
+      <c r="G61" s="10" t="s">
         <v>190</v>
       </c>
-      <c r="H61" s="11" t="s">
+      <c r="H61" s="17" t="s">
         <v>383</v>
       </c>
-      <c r="I61" s="14"/>
-      <c r="K61" s="6"/>
-    </row>
-    <row r="62" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A62" s="6" t="s">
+      <c r="I61" s="12"/>
+      <c r="K61" s="10"/>
+    </row>
+    <row r="62" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A62" s="10" t="s">
         <v>194</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="B62" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D62" s="9"/>
-      <c r="E62" s="4" t="s">
+      <c r="E62" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F62" s="4"/>
-      <c r="G62" s="6" t="s">
+      <c r="F62" s="7"/>
+      <c r="G62" s="10" t="s">
         <v>193</v>
       </c>
-      <c r="H62" s="11" t="s">
+      <c r="H62" s="17" t="s">
         <v>384</v>
       </c>
-      <c r="I62" s="14"/>
-      <c r="K62" s="6"/>
-    </row>
-    <row r="63" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A63" s="6" t="s">
+      <c r="I62" s="12"/>
+      <c r="K62" s="10"/>
+    </row>
+    <row r="63" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A63" s="10" t="s">
         <v>197</v>
       </c>
-      <c r="B63" s="4" t="s">
+      <c r="B63" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="8" t="s">
         <v>59</v>
       </c>
       <c r="D63" s="9"/>
-      <c r="E63" s="4" t="s">
+      <c r="E63" s="7" t="s">
         <v>60</v>
       </c>
-      <c r="F63" s="4"/>
-      <c r="G63" s="6" t="s">
+      <c r="F63" s="7"/>
+      <c r="G63" s="10" t="s">
         <v>196</v>
       </c>
-      <c r="H63" s="11" t="s">
+      <c r="H63" s="17" t="s">
         <v>385</v>
       </c>
-      <c r="I63" s="14"/>
-      <c r="K63" s="6"/>
-    </row>
-    <row r="64" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A64" s="6" t="s">
+      <c r="I63" s="12"/>
+      <c r="K63" s="10"/>
+    </row>
+    <row r="64" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A64" s="10" t="s">
         <v>199</v>
       </c>
-      <c r="B64" s="4" t="s">
+      <c r="B64" s="7" t="s">
         <v>200</v>
       </c>
-      <c r="C64" s="5" t="s">
+      <c r="C64" s="8" t="s">
         <v>157</v>
       </c>
       <c r="D64" s="9"/>
-      <c r="E64" s="4" t="s">
+      <c r="E64" s="7" t="s">
         <v>158</v>
       </c>
-      <c r="F64" s="4"/>
-      <c r="G64" s="6" t="s">
+      <c r="F64" s="7"/>
+      <c r="G64" s="10" t="s">
         <v>198</v>
       </c>
-      <c r="H64" s="11" t="s">
+      <c r="H64" s="17" t="s">
         <v>386</v>
       </c>
-      <c r="I64" s="14"/>
-      <c r="K64" s="6"/>
-    </row>
-    <row r="65" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A65" s="6" t="s">
+      <c r="I64" s="12"/>
+      <c r="K64" s="10"/>
+    </row>
+    <row r="65" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A65" s="10" t="s">
         <v>202</v>
       </c>
-      <c r="B65" s="4" t="s">
+      <c r="B65" s="7" t="s">
         <v>203</v>
       </c>
-      <c r="C65" s="5" t="s">
+      <c r="C65" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D65" s="9"/>
-      <c r="E65" s="4" t="s">
+      <c r="E65" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="F65" s="4"/>
-      <c r="G65" s="6" t="s">
+      <c r="F65" s="7"/>
+      <c r="G65" s="10" t="s">
         <v>201</v>
       </c>
-      <c r="H65" s="11" t="s">
+      <c r="H65" s="17" t="s">
         <v>387</v>
       </c>
-      <c r="I65" s="14"/>
-      <c r="K65" s="6"/>
-    </row>
-    <row r="66" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A66" s="6" t="s">
+      <c r="I65" s="12"/>
+      <c r="K65" s="10"/>
+    </row>
+    <row r="66" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A66" s="10" t="s">
         <v>206</v>
       </c>
-      <c r="B66" s="4" t="s">
+      <c r="B66" s="7" t="s">
         <v>207</v>
       </c>
-      <c r="C66" s="5" t="s">
+      <c r="C66" s="8" t="s">
         <v>208</v>
       </c>
       <c r="D66" s="9"/>
-      <c r="E66" s="4" t="s">
+      <c r="E66" s="7" t="s">
         <v>209</v>
       </c>
-      <c r="F66" s="4"/>
-      <c r="G66" s="6" t="s">
+      <c r="F66" s="7"/>
+      <c r="G66" s="10" t="s">
         <v>205</v>
       </c>
-      <c r="H66" s="11" t="s">
+      <c r="H66" s="17" t="s">
         <v>388</v>
       </c>
-      <c r="I66" s="14"/>
-      <c r="K66" s="6"/>
-    </row>
-    <row r="67" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A67" s="6" t="s">
+      <c r="I66" s="12"/>
+      <c r="K66" s="10"/>
+    </row>
+    <row r="67" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A67" s="10" t="s">
         <v>211</v>
       </c>
-      <c r="B67" s="4" t="s">
+      <c r="B67" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C67" s="5" t="s">
+      <c r="C67" s="8" t="s">
         <v>54</v>
       </c>
       <c r="D67" s="9"/>
-      <c r="E67" s="4" t="s">
+      <c r="E67" s="7" t="s">
         <v>55</v>
       </c>
-      <c r="F67" s="4"/>
-      <c r="G67" s="6" t="s">
+      <c r="F67" s="7"/>
+      <c r="G67" s="10" t="s">
         <v>210</v>
       </c>
-      <c r="H67" s="11" t="s">
+      <c r="H67" s="17" t="s">
         <v>389</v>
       </c>
-      <c r="I67" s="14"/>
-      <c r="K67" s="6"/>
-    </row>
-    <row r="68" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A68" s="6" t="s">
+      <c r="I67" s="12"/>
+      <c r="K67" s="10"/>
+    </row>
+    <row r="68" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A68" s="10" t="s">
         <v>213</v>
       </c>
-      <c r="B68" s="4" t="s">
+      <c r="B68" s="7" t="s">
         <v>214</v>
       </c>
-      <c r="C68" s="5" t="s">
+      <c r="C68" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D68" s="9"/>
-      <c r="E68" s="4" t="s">
+      <c r="E68" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F68" s="4"/>
-      <c r="G68" s="6" t="s">
+      <c r="F68" s="7"/>
+      <c r="G68" s="10" t="s">
         <v>212</v>
       </c>
-      <c r="H68" s="11" t="s">
+      <c r="H68" s="17" t="s">
         <v>390</v>
       </c>
-      <c r="I68" s="14"/>
-      <c r="K68" s="6"/>
-    </row>
-    <row r="69" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A69" s="6" t="s">
+      <c r="I68" s="12"/>
+      <c r="K68" s="10"/>
+    </row>
+    <row r="69" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A69" s="10" t="s">
         <v>216</v>
       </c>
-      <c r="B69" s="4" t="s">
+      <c r="B69" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C69" s="5" t="s">
+      <c r="C69" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D69" s="9"/>
-      <c r="E69" s="4" t="s">
+      <c r="E69" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F69" s="4"/>
-      <c r="G69" s="6" t="s">
+      <c r="F69" s="7"/>
+      <c r="G69" s="10" t="s">
         <v>215</v>
       </c>
-      <c r="H69" s="11" t="s">
+      <c r="H69" s="17" t="s">
         <v>391</v>
       </c>
-      <c r="I69" s="14"/>
-      <c r="K69" s="6"/>
-    </row>
-    <row r="70" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A70" s="6" t="s">
+      <c r="I69" s="12"/>
+      <c r="K69" s="10"/>
+    </row>
+    <row r="70" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A70" s="10" t="s">
         <v>218</v>
       </c>
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C70" s="5" t="s">
+      <c r="C70" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D70" s="9"/>
-      <c r="E70" s="4" t="s">
+      <c r="E70" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F70" s="4"/>
-      <c r="G70" s="6" t="s">
+      <c r="F70" s="7"/>
+      <c r="G70" s="10" t="s">
         <v>217</v>
       </c>
-      <c r="H70" s="11" t="s">
+      <c r="H70" s="17" t="s">
         <v>392</v>
       </c>
-      <c r="I70" s="14"/>
-      <c r="K70" s="6"/>
-    </row>
-    <row r="71" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A71" s="6" t="s">
+      <c r="I70" s="12"/>
+      <c r="K70" s="10"/>
+    </row>
+    <row r="71" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A71" s="10" t="s">
         <v>220</v>
       </c>
-      <c r="B71" s="4" t="s">
+      <c r="B71" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C71" s="5" t="s">
+      <c r="C71" s="8" t="s">
         <v>171</v>
       </c>
       <c r="D71" s="9"/>
-      <c r="E71" s="4" t="s">
+      <c r="E71" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F71" s="4"/>
-      <c r="G71" s="6" t="s">
+      <c r="F71" s="7"/>
+      <c r="G71" s="10" t="s">
         <v>219</v>
       </c>
-      <c r="H71" s="11" t="s">
+      <c r="H71" s="17" t="s">
         <v>393</v>
       </c>
-      <c r="I71" s="14"/>
-      <c r="K71" s="6"/>
-    </row>
-    <row r="72" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A72" s="6" t="s">
+      <c r="I71" s="12"/>
+      <c r="K71" s="10"/>
+    </row>
+    <row r="72" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="10" t="s">
         <v>222</v>
       </c>
-      <c r="B72" s="4" t="s">
+      <c r="B72" s="7" t="s">
         <v>223</v>
       </c>
-      <c r="C72" s="5" t="s">
+      <c r="C72" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D72" s="9"/>
-      <c r="E72" s="4" t="s">
+      <c r="E72" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F72" s="4"/>
-      <c r="G72" s="6" t="s">
+      <c r="F72" s="7"/>
+      <c r="G72" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="H72" s="11" t="s">
+      <c r="H72" s="17" t="s">
         <v>394</v>
       </c>
-      <c r="I72" s="14"/>
-      <c r="K72" s="6"/>
-    </row>
-    <row r="73" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A73" s="6" t="s">
+      <c r="I72" s="12"/>
+      <c r="K72" s="10"/>
+    </row>
+    <row r="73" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="10" t="s">
         <v>225</v>
       </c>
-      <c r="B73" s="4" t="s">
+      <c r="B73" s="7" t="s">
         <v>50</v>
       </c>
-      <c r="C73" s="5" t="s">
+      <c r="C73" s="8" t="s">
         <v>171</v>
       </c>
       <c r="D73" s="9"/>
-      <c r="E73" s="4" t="s">
+      <c r="E73" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F73" s="4"/>
-      <c r="G73" s="6" t="s">
+      <c r="F73" s="7"/>
+      <c r="G73" s="10" t="s">
         <v>224</v>
       </c>
-      <c r="H73" s="11" t="s">
+      <c r="H73" s="17" t="s">
         <v>395</v>
       </c>
-      <c r="I73" s="14"/>
-      <c r="K73" s="6"/>
-    </row>
-    <row r="74" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A74" s="6" t="s">
+      <c r="I73" s="12"/>
+      <c r="K73" s="10"/>
+    </row>
+    <row r="74" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="10" t="s">
         <v>227</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="7" t="s">
         <v>228</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="8" t="s">
         <v>183</v>
       </c>
       <c r="D74" s="9"/>
-      <c r="E74" s="4" t="s">
+      <c r="E74" s="7" t="s">
         <v>229</v>
       </c>
-      <c r="F74" s="4"/>
-      <c r="G74" s="6" t="s">
+      <c r="F74" s="7"/>
+      <c r="G74" s="10" t="s">
         <v>226</v>
       </c>
-      <c r="H74" s="11" t="s">
+      <c r="H74" s="17" t="s">
         <v>396</v>
       </c>
-      <c r="I74" s="14"/>
-      <c r="K74" s="6"/>
-    </row>
-    <row r="75" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A75" s="6" t="s">
+      <c r="I74" s="12"/>
+      <c r="K74" s="10"/>
+    </row>
+    <row r="75" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="B75" s="4" t="s">
+      <c r="B75" s="7" t="s">
         <v>36</v>
       </c>
-      <c r="C75" s="5" t="s">
+      <c r="C75" s="8" t="s">
         <v>181</v>
       </c>
       <c r="D75" s="9"/>
-      <c r="E75" s="4" t="s">
+      <c r="E75" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F75" s="4"/>
-      <c r="G75" s="6" t="s">
+      <c r="F75" s="7"/>
+      <c r="G75" s="10" t="s">
         <v>230</v>
       </c>
-      <c r="H75" s="11" t="s">
+      <c r="H75" s="17" t="s">
         <v>397</v>
       </c>
-      <c r="I75" s="14"/>
-      <c r="K75" s="6"/>
-    </row>
-    <row r="76" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A76" s="6" t="s">
+      <c r="I75" s="12"/>
+      <c r="K75" s="10"/>
+    </row>
+    <row r="76" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="10" t="s">
         <v>233</v>
       </c>
-      <c r="B76" s="4" t="s">
+      <c r="B76" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C76" s="5" t="s">
+      <c r="C76" s="8" t="s">
         <v>171</v>
       </c>
       <c r="D76" s="9"/>
-      <c r="E76" s="4" t="s">
+      <c r="E76" s="7" t="s">
         <v>172</v>
       </c>
-      <c r="F76" s="4"/>
-      <c r="G76" s="6" t="s">
+      <c r="F76" s="7"/>
+      <c r="G76" s="10" t="s">
         <v>232</v>
       </c>
-      <c r="H76" s="11" t="s">
+      <c r="H76" s="17" t="s">
         <v>398</v>
       </c>
-      <c r="I76" s="14"/>
-      <c r="K76" s="6"/>
-    </row>
-    <row r="77" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A77" s="6" t="s">
+      <c r="I76" s="12"/>
+      <c r="K76" s="10"/>
+    </row>
+    <row r="77" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="10" t="s">
         <v>235</v>
       </c>
-      <c r="B77" s="4" t="s">
+      <c r="B77" s="7" t="s">
         <v>236</v>
       </c>
-      <c r="C77" s="5" t="s">
+      <c r="C77" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D77" s="9"/>
-      <c r="E77" s="4" t="s">
+      <c r="E77" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F77" s="4"/>
-      <c r="G77" s="6" t="s">
+      <c r="F77" s="7"/>
+      <c r="G77" s="10" t="s">
         <v>234</v>
       </c>
-      <c r="H77" s="11" t="s">
+      <c r="H77" s="17" t="s">
         <v>399</v>
       </c>
-      <c r="I77" s="14"/>
-      <c r="K77" s="6"/>
-    </row>
-    <row r="78" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A78" s="6" t="s">
+      <c r="I77" s="12"/>
+      <c r="K77" s="10"/>
+    </row>
+    <row r="78" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="10" t="s">
         <v>238</v>
       </c>
-      <c r="B78" s="4"/>
-      <c r="C78" s="5"/>
+      <c r="B78" s="7"/>
+      <c r="C78" s="8"/>
       <c r="D78" s="9"/>
-      <c r="E78" s="4"/>
-      <c r="F78" s="4"/>
-      <c r="G78" s="6" t="s">
+      <c r="E78" s="7"/>
+      <c r="F78" s="7"/>
+      <c r="G78" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="H78" s="11" t="s">
+      <c r="H78" s="17" t="s">
         <v>463</v>
       </c>
-      <c r="I78" s="14"/>
-      <c r="K78" s="6"/>
-    </row>
-    <row r="79" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A79" s="6" t="s">
+      <c r="I78" s="12"/>
+      <c r="K78" s="10"/>
+    </row>
+    <row r="79" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="10" t="s">
         <v>240</v>
       </c>
-      <c r="B79" s="4" t="s">
+      <c r="B79" s="7" t="s">
         <v>241</v>
       </c>
-      <c r="C79" s="5" t="s">
+      <c r="C79" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D79" s="9"/>
-      <c r="E79" s="4" t="s">
+      <c r="E79" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="F79" s="4"/>
-      <c r="G79" s="6" t="s">
+      <c r="F79" s="7"/>
+      <c r="G79" s="10" t="s">
         <v>239</v>
       </c>
-      <c r="H79" s="11" t="s">
+      <c r="H79" s="17" t="s">
         <v>400</v>
       </c>
-      <c r="I79" s="14"/>
-      <c r="K79" s="6"/>
-    </row>
-    <row r="80" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A80" s="6" t="s">
+      <c r="I79" s="12"/>
+      <c r="K79" s="10"/>
+    </row>
+    <row r="80" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="10" t="s">
         <v>243</v>
       </c>
-      <c r="B80" s="4" t="s">
+      <c r="B80" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C80" s="5" t="s">
+      <c r="C80" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D80" s="9"/>
-      <c r="E80" s="4" t="s">
+      <c r="E80" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F80" s="4"/>
-      <c r="G80" s="6" t="s">
+      <c r="F80" s="7"/>
+      <c r="G80" s="10" t="s">
         <v>242</v>
       </c>
-      <c r="H80" s="11" t="s">
+      <c r="H80" s="17" t="s">
         <v>401</v>
       </c>
-      <c r="I80" s="14"/>
-      <c r="K80" s="6"/>
-    </row>
-    <row r="81" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A81" s="6" t="s">
+      <c r="I80" s="12"/>
+      <c r="K80" s="10"/>
+    </row>
+    <row r="81" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="10" t="s">
         <v>245</v>
       </c>
-      <c r="B81" s="4" t="s">
+      <c r="B81" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C81" s="5" t="s">
+      <c r="C81" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D81" s="9"/>
-      <c r="E81" s="4" t="s">
+      <c r="E81" s="7" t="s">
         <v>37</v>
       </c>
-      <c r="F81" s="4"/>
-      <c r="G81" s="6" t="s">
+      <c r="F81" s="7"/>
+      <c r="G81" s="10" t="s">
         <v>244</v>
       </c>
-      <c r="H81" s="11" t="s">
+      <c r="H81" s="17" t="s">
         <v>402</v>
       </c>
-      <c r="I81" s="14"/>
-      <c r="K81" s="6"/>
-    </row>
-    <row r="82" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A82" s="6" t="s">
+      <c r="I81" s="12"/>
+      <c r="K81" s="10"/>
+    </row>
+    <row r="82" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="10" t="s">
         <v>247</v>
       </c>
-      <c r="B82" s="4" t="s">
+      <c r="B82" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C82" s="5" t="s">
+      <c r="C82" s="8" t="s">
         <v>181</v>
       </c>
       <c r="D82" s="9"/>
-      <c r="E82" s="4" t="s">
+      <c r="E82" s="7" t="s">
         <v>101</v>
       </c>
-      <c r="F82" s="4"/>
-      <c r="G82" s="6" t="s">
+      <c r="F82" s="7"/>
+      <c r="G82" s="10" t="s">
         <v>246</v>
       </c>
-      <c r="H82" s="11" t="s">
+      <c r="H82" s="17" t="s">
         <v>403</v>
       </c>
-      <c r="I82" s="14"/>
-      <c r="K82" s="6"/>
-    </row>
-    <row r="83" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A83" s="6" t="s">
+      <c r="I82" s="12"/>
+      <c r="K82" s="10"/>
+    </row>
+    <row r="83" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A83" s="10" t="s">
         <v>250</v>
       </c>
-      <c r="B83" s="4" t="s">
+      <c r="B83" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="C83" s="5" t="s">
+      <c r="C83" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D83" s="9"/>
-      <c r="E83" s="4" t="s">
+      <c r="E83" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F83" s="4"/>
-      <c r="G83" s="6" t="s">
+      <c r="F83" s="7"/>
+      <c r="G83" s="10" t="s">
         <v>249</v>
       </c>
-      <c r="H83" s="11" t="s">
+      <c r="H83" s="17" t="s">
         <v>404</v>
       </c>
-      <c r="I83" s="14"/>
-      <c r="K83" s="6"/>
-    </row>
-    <row r="84" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A84" s="6" t="s">
+      <c r="I83" s="12"/>
+      <c r="K83" s="10"/>
+    </row>
+    <row r="84" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A84" s="10" t="s">
         <v>253</v>
       </c>
-      <c r="B84" s="4" t="s">
+      <c r="B84" s="7" t="s">
         <v>254</v>
       </c>
-      <c r="C84" s="5" t="s">
+      <c r="C84" s="8" t="s">
         <v>237</v>
       </c>
       <c r="D84" s="9"/>
-      <c r="E84" s="4" t="s">
+      <c r="E84" s="7" t="s">
         <v>151</v>
       </c>
-      <c r="F84" s="4"/>
-      <c r="G84" s="6" t="s">
+      <c r="F84" s="7"/>
+      <c r="G84" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="H84" s="11" t="s">
+      <c r="H84" s="17" t="s">
         <v>405</v>
       </c>
-      <c r="I84" s="14"/>
-      <c r="K84" s="6"/>
-    </row>
-    <row r="85" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A85" s="6" t="s">
+      <c r="I84" s="12"/>
+      <c r="K84" s="10"/>
+    </row>
+    <row r="85" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A85" s="10" t="s">
         <v>256</v>
       </c>
-      <c r="B85" s="4" t="s">
+      <c r="B85" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C85" s="5" t="s">
+      <c r="C85" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D85" s="9"/>
-      <c r="E85" s="4" t="s">
+      <c r="E85" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F85" s="4"/>
-      <c r="G85" s="6" t="s">
+      <c r="F85" s="7"/>
+      <c r="G85" s="10" t="s">
         <v>255</v>
       </c>
-      <c r="H85" s="11" t="s">
+      <c r="H85" s="17" t="s">
         <v>406</v>
       </c>
-      <c r="I85" s="14"/>
-      <c r="K85" s="6"/>
-    </row>
-    <row r="86" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A86" s="6" t="s">
+      <c r="I85" s="12"/>
+      <c r="K85" s="10"/>
+    </row>
+    <row r="86" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A86" s="10" t="s">
         <v>258</v>
       </c>
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="7" t="s">
         <v>104</v>
       </c>
-      <c r="C86" s="5" t="s">
+      <c r="C86" s="8" t="s">
         <v>182</v>
       </c>
       <c r="D86" s="9"/>
-      <c r="E86" s="4" t="s">
+      <c r="E86" s="7" t="s">
         <v>204</v>
       </c>
-      <c r="F86" s="4"/>
-      <c r="G86" s="6" t="s">
+      <c r="F86" s="7"/>
+      <c r="G86" s="10" t="s">
         <v>257</v>
       </c>
-      <c r="H86" s="11" t="s">
+      <c r="H86" s="17" t="s">
         <v>407</v>
       </c>
-      <c r="I86" s="14"/>
-      <c r="K86" s="6"/>
-    </row>
-    <row r="87" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A87" s="6" t="s">
+      <c r="I86" s="12"/>
+      <c r="K86" s="10"/>
+    </row>
+    <row r="87" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A87" s="10" t="s">
         <v>260</v>
       </c>
-      <c r="B87" s="4" t="s">
+      <c r="B87" s="7" t="s">
         <v>261</v>
       </c>
-      <c r="C87" s="5" t="s">
+      <c r="C87" s="8" t="s">
         <v>262</v>
       </c>
       <c r="D87" s="9"/>
-      <c r="E87" s="4" t="s">
+      <c r="E87" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="F87" s="4"/>
-      <c r="G87" s="6" t="s">
+      <c r="F87" s="7"/>
+      <c r="G87" s="10" t="s">
         <v>259</v>
       </c>
-      <c r="H87" s="11" t="s">
+      <c r="H87" s="17" t="s">
         <v>408</v>
       </c>
-      <c r="I87" s="14"/>
-      <c r="K87" s="6"/>
-    </row>
-    <row r="88" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A88" s="6" t="s">
+      <c r="I87" s="12"/>
+      <c r="K87" s="10"/>
+    </row>
+    <row r="88" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A88" s="10" t="s">
         <v>265</v>
       </c>
-      <c r="B88" s="4" t="s">
+      <c r="B88" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="C88" s="5" t="s">
+      <c r="C88" s="8" t="s">
         <v>107</v>
       </c>
       <c r="D88" s="9"/>
-      <c r="E88" s="4" t="s">
+      <c r="E88" s="7" t="s">
         <v>251</v>
       </c>
-      <c r="F88" s="4"/>
-      <c r="G88" s="6" t="s">
+      <c r="F88" s="7"/>
+      <c r="G88" s="10" t="s">
         <v>264</v>
       </c>
-      <c r="H88" s="11" t="s">
+      <c r="H88" s="17" t="s">
         <v>409</v>
       </c>
-      <c r="I88" s="14"/>
-      <c r="K88" s="6"/>
-    </row>
-    <row r="89" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A89" s="6" t="s">
+      <c r="I88" s="12"/>
+      <c r="K88" s="10"/>
+    </row>
+    <row r="89" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A89" s="10" t="s">
         <v>267</v>
       </c>
-      <c r="B89" s="4" t="s">
+      <c r="B89" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C89" s="5" t="s">
+      <c r="C89" s="8" t="s">
         <v>268</v>
       </c>
       <c r="D89" s="9"/>
-      <c r="E89" s="4" t="s">
+      <c r="E89" s="7" t="s">
         <v>269</v>
       </c>
-      <c r="F89" s="4"/>
-      <c r="G89" s="6" t="s">
+      <c r="F89" s="7"/>
+      <c r="G89" s="10" t="s">
         <v>266</v>
       </c>
-      <c r="H89" s="11" t="s">
+      <c r="H89" s="17" t="s">
         <v>410</v>
       </c>
-      <c r="I89" s="14"/>
-      <c r="K89" s="6"/>
-    </row>
-    <row r="90" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A90" s="6" t="s">
+      <c r="I89" s="12"/>
+      <c r="K89" s="10"/>
+    </row>
+    <row r="90" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A90" s="10" t="s">
         <v>271</v>
       </c>
-      <c r="B90" s="4" t="s">
+      <c r="B90" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C90" s="5" t="s">
+      <c r="C90" s="8" t="s">
         <v>262</v>
       </c>
       <c r="D90" s="9"/>
-      <c r="E90" s="4" t="s">
+      <c r="E90" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="F90" s="4"/>
-      <c r="G90" s="6" t="s">
+      <c r="F90" s="7"/>
+      <c r="G90" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="H90" s="11" t="s">
+      <c r="H90" s="17" t="s">
         <v>411</v>
       </c>
-      <c r="I90" s="14"/>
-      <c r="K90" s="6"/>
-    </row>
-    <row r="91" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A91" s="6" t="s">
+      <c r="I90" s="12"/>
+      <c r="K90" s="10"/>
+    </row>
+    <row r="91" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A91" s="10" t="s">
         <v>273</v>
       </c>
-      <c r="B91" s="4" t="s">
+      <c r="B91" s="7" t="s">
         <v>274</v>
       </c>
-      <c r="C91" s="5" t="s">
+      <c r="C91" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D91" s="9"/>
-      <c r="E91" s="4" t="s">
+      <c r="E91" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F91" s="4"/>
-      <c r="G91" s="6" t="s">
+      <c r="F91" s="7"/>
+      <c r="G91" s="10" t="s">
         <v>272</v>
       </c>
-      <c r="H91" s="11" t="s">
+      <c r="H91" s="17" t="s">
         <v>412</v>
       </c>
-      <c r="I91" s="14"/>
-      <c r="K91" s="6"/>
-    </row>
-    <row r="92" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A92" s="6" t="s">
+      <c r="I91" s="12"/>
+      <c r="K91" s="10"/>
+    </row>
+    <row r="92" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A92" s="10" t="s">
         <v>276</v>
       </c>
-      <c r="B92" s="4" t="s">
+      <c r="B92" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C92" s="5" t="s">
+      <c r="C92" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D92" s="9"/>
-      <c r="E92" s="4" t="s">
+      <c r="E92" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F92" s="4"/>
-      <c r="G92" s="6" t="s">
+      <c r="F92" s="7"/>
+      <c r="G92" s="10" t="s">
         <v>275</v>
       </c>
-      <c r="H92" s="11" t="s">
+      <c r="H92" s="17" t="s">
         <v>413</v>
       </c>
-      <c r="I92" s="14"/>
-      <c r="K92" s="6"/>
-    </row>
-    <row r="93" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A93" s="6" t="s">
+      <c r="I92" s="12"/>
+      <c r="K92" s="10"/>
+    </row>
+    <row r="93" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A93" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="B93" s="4" t="s">
+      <c r="B93" s="7" t="s">
         <v>279</v>
       </c>
-      <c r="C93" s="5" t="s">
+      <c r="C93" s="8" t="s">
         <v>280</v>
       </c>
       <c r="D93" s="9"/>
-      <c r="E93" s="4" t="s">
+      <c r="E93" s="7" t="s">
         <v>281</v>
       </c>
-      <c r="F93" s="4"/>
-      <c r="G93" s="6" t="s">
+      <c r="F93" s="7"/>
+      <c r="G93" s="10" t="s">
         <v>277</v>
       </c>
-      <c r="H93" s="11" t="s">
+      <c r="H93" s="17" t="s">
         <v>414</v>
       </c>
-      <c r="I93" s="14"/>
-      <c r="K93" s="6"/>
-    </row>
-    <row r="94" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A94" s="6" t="s">
+      <c r="I93" s="12"/>
+      <c r="K93" s="10"/>
+    </row>
+    <row r="94" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A94" s="10" t="s">
         <v>283</v>
       </c>
-      <c r="B94" s="4" t="s">
+      <c r="B94" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="C94" s="5" t="s">
+      <c r="C94" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D94" s="9"/>
-      <c r="E94" s="4" t="s">
+      <c r="E94" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F94" s="4"/>
-      <c r="G94" s="6" t="s">
+      <c r="F94" s="7"/>
+      <c r="G94" s="10" t="s">
         <v>282</v>
       </c>
-      <c r="H94" s="11" t="s">
+      <c r="H94" s="17" t="s">
         <v>415</v>
       </c>
-      <c r="I94" s="14"/>
-      <c r="K94" s="6"/>
-    </row>
-    <row r="95" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A95" s="6" t="s">
+      <c r="I94" s="12"/>
+      <c r="K94" s="10"/>
+    </row>
+    <row r="95" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A95" s="10" t="s">
         <v>285</v>
       </c>
-      <c r="B95" s="4" t="s">
+      <c r="B95" s="7" t="s">
         <v>286</v>
       </c>
-      <c r="C95" s="5" t="s">
+      <c r="C95" s="8" t="s">
         <v>262</v>
       </c>
       <c r="D95" s="9"/>
-      <c r="E95" s="4" t="s">
+      <c r="E95" s="7" t="s">
         <v>263</v>
       </c>
-      <c r="F95" s="4"/>
-      <c r="G95" s="6" t="s">
+      <c r="F95" s="7"/>
+      <c r="G95" s="10" t="s">
         <v>284</v>
       </c>
-      <c r="H95" s="11" t="s">
+      <c r="H95" s="17" t="s">
         <v>416</v>
       </c>
-      <c r="I95" s="14"/>
-      <c r="K95" s="6"/>
-    </row>
-    <row r="96" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A96" s="6" t="s">
+      <c r="I95" s="12"/>
+      <c r="K95" s="10"/>
+    </row>
+    <row r="96" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A96" s="10" t="s">
         <v>288</v>
       </c>
-      <c r="B96" s="4" t="s">
+      <c r="B96" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="C96" s="5" t="s">
+      <c r="C96" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D96" s="9"/>
-      <c r="E96" s="4" t="s">
+      <c r="E96" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F96" s="4"/>
-      <c r="G96" s="6" t="s">
+      <c r="F96" s="7"/>
+      <c r="G96" s="10" t="s">
         <v>287</v>
       </c>
-      <c r="H96" s="11" t="s">
+      <c r="H96" s="17" t="s">
         <v>417</v>
       </c>
-      <c r="I96" s="14"/>
-      <c r="K96" s="6"/>
-    </row>
-    <row r="97" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A97" s="6" t="s">
+      <c r="I96" s="12"/>
+      <c r="K96" s="10"/>
+    </row>
+    <row r="97" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A97" s="10" t="s">
         <v>290</v>
       </c>
-      <c r="B97" s="4" t="s">
+      <c r="B97" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C97" s="5" t="s">
+      <c r="C97" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D97" s="9"/>
-      <c r="E97" s="4" t="s">
+      <c r="E97" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F97" s="4"/>
-      <c r="G97" s="6" t="s">
+      <c r="F97" s="7"/>
+      <c r="G97" s="10" t="s">
         <v>289</v>
       </c>
-      <c r="H97" s="11" t="s">
+      <c r="H97" s="17" t="s">
         <v>418</v>
       </c>
-      <c r="I97" s="14"/>
-      <c r="K97" s="6"/>
-    </row>
-    <row r="98" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A98" s="6" t="s">
+      <c r="I97" s="12"/>
+      <c r="K97" s="10"/>
+    </row>
+    <row r="98" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A98" s="10" t="s">
         <v>293</v>
       </c>
-      <c r="B98" s="4" t="s">
+      <c r="B98" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C98" s="5" t="s">
+      <c r="C98" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D98" s="9"/>
-      <c r="E98" s="4" t="s">
+      <c r="E98" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F98" s="4"/>
-      <c r="G98" s="6" t="s">
+      <c r="F98" s="7"/>
+      <c r="G98" s="10" t="s">
         <v>292</v>
       </c>
-      <c r="H98" s="11" t="s">
+      <c r="H98" s="17" t="s">
         <v>419</v>
       </c>
-      <c r="I98" s="14"/>
-      <c r="K98" s="6"/>
-    </row>
-    <row r="99" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A99" s="6" t="s">
+      <c r="I98" s="12"/>
+      <c r="K98" s="10"/>
+    </row>
+    <row r="99" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A99" s="10" t="s">
         <v>295</v>
       </c>
-      <c r="B99" s="4" t="s">
+      <c r="B99" s="7" t="s">
         <v>195</v>
       </c>
-      <c r="C99" s="5" t="s">
+      <c r="C99" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D99" s="9"/>
-      <c r="E99" s="4" t="s">
+      <c r="E99" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F99" s="4"/>
-      <c r="G99" s="6" t="s">
+      <c r="F99" s="7"/>
+      <c r="G99" s="10" t="s">
         <v>294</v>
       </c>
-      <c r="H99" s="11" t="s">
+      <c r="H99" s="17" t="s">
         <v>420</v>
       </c>
-      <c r="I99" s="14"/>
-      <c r="K99" s="6"/>
-    </row>
-    <row r="100" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A100" s="6" t="s">
+      <c r="I99" s="12"/>
+      <c r="K99" s="10"/>
+    </row>
+    <row r="100" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A100" s="10" t="s">
         <v>298</v>
       </c>
-      <c r="B100" s="4" t="s">
+      <c r="B100" s="7" t="s">
         <v>161</v>
       </c>
-      <c r="C100" s="5" t="s">
+      <c r="C100" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D100" s="9"/>
-      <c r="E100" s="4" t="s">
+      <c r="E100" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F100" s="4"/>
-      <c r="G100" s="6" t="s">
+      <c r="F100" s="7"/>
+      <c r="G100" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="H100" s="11" t="s">
+      <c r="H100" s="17" t="s">
         <v>421</v>
       </c>
-      <c r="I100" s="14"/>
-      <c r="K100" s="6"/>
-    </row>
-    <row r="101" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A101" s="6" t="s">
+      <c r="I100" s="12"/>
+      <c r="K100" s="10"/>
+    </row>
+    <row r="101" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A101" s="10" t="s">
         <v>300</v>
       </c>
-      <c r="B101" s="4" t="s">
+      <c r="B101" s="7" t="s">
         <v>291</v>
       </c>
-      <c r="C101" s="5" t="s">
+      <c r="C101" s="8" t="s">
         <v>9</v>
       </c>
       <c r="D101" s="9"/>
-      <c r="E101" s="4" t="s">
+      <c r="E101" s="7" t="s">
         <v>10</v>
       </c>
-      <c r="F101" s="4"/>
-      <c r="G101" s="6" t="s">
+      <c r="F101" s="7"/>
+      <c r="G101" s="10" t="s">
         <v>299</v>
       </c>
-      <c r="H101" s="11" t="s">
+      <c r="H101" s="17" t="s">
         <v>422</v>
       </c>
-      <c r="I101" s="14"/>
-      <c r="K101" s="6"/>
-    </row>
-    <row r="102" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A102" s="6" t="s">
+      <c r="I101" s="12"/>
+      <c r="K101" s="10"/>
+    </row>
+    <row r="102" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A102" s="10" t="s">
         <v>302</v>
       </c>
-      <c r="B102" s="4" t="s">
+      <c r="B102" s="7" t="s">
         <v>94</v>
       </c>
-      <c r="C102" s="5" t="s">
+      <c r="C102" s="8" t="s">
         <v>39</v>
       </c>
       <c r="D102" s="9"/>
-      <c r="E102" s="4" t="s">
+      <c r="E102" s="7" t="s">
         <v>40</v>
       </c>
-      <c r="F102" s="4"/>
-      <c r="G102" s="6" t="s">
+      <c r="F102" s="7"/>
+      <c r="G102" s="10" t="s">
         <v>301</v>
       </c>
-      <c r="H102" s="11" t="s">
+      <c r="H102" s="17" t="s">
         <v>423</v>
       </c>
-      <c r="I102" s="14"/>
-      <c r="K102" s="6"/>
-    </row>
-    <row r="103" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A103" s="6" t="s">
+      <c r="I102" s="12"/>
+      <c r="K102" s="10"/>
+    </row>
+    <row r="103" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A103" s="10" t="s">
         <v>304</v>
       </c>
-      <c r="B103" s="4" t="s">
+      <c r="B103" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C103" s="5" t="s">
+      <c r="C103" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D103" s="9"/>
-      <c r="E103" s="4" t="s">
+      <c r="E103" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F103" s="4"/>
-      <c r="G103" s="6" t="s">
+      <c r="F103" s="7"/>
+      <c r="G103" s="10" t="s">
         <v>303</v>
       </c>
-      <c r="H103" s="11" t="s">
+      <c r="H103" s="17" t="s">
         <v>424</v>
       </c>
-      <c r="I103" s="14"/>
-      <c r="K103" s="6"/>
-    </row>
-    <row r="104" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A104" s="6" t="s">
+      <c r="I103" s="12"/>
+      <c r="K103" s="10"/>
+    </row>
+    <row r="104" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A104" s="10" t="s">
         <v>306</v>
       </c>
-      <c r="B104" s="4" t="s">
+      <c r="B104" s="7" t="s">
         <v>85</v>
       </c>
-      <c r="C104" s="5" t="s">
+      <c r="C104" s="8" t="s">
         <v>86</v>
       </c>
       <c r="D104" s="9"/>
-      <c r="E104" s="4" t="s">
+      <c r="E104" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="F104" s="4"/>
-      <c r="G104" s="6" t="s">
+      <c r="F104" s="7"/>
+      <c r="G104" s="10" t="s">
         <v>305</v>
       </c>
-      <c r="H104" s="11" t="s">
+      <c r="H104" s="17" t="s">
         <v>425</v>
       </c>
-      <c r="I104" s="14"/>
-      <c r="K104" s="6"/>
-    </row>
-    <row r="105" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A105" s="6" t="s">
+      <c r="I104" s="12"/>
+      <c r="K104" s="10"/>
+    </row>
+    <row r="105" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A105" s="10" t="s">
         <v>308</v>
       </c>
-      <c r="B105" s="4" t="s">
+      <c r="B105" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="C105" s="5" t="s">
+      <c r="C105" s="8" t="s">
         <v>73</v>
       </c>
       <c r="D105" s="9"/>
-      <c r="E105" s="4" t="s">
+      <c r="E105" s="7" t="s">
         <v>74</v>
       </c>
-      <c r="F105" s="4"/>
-      <c r="G105" s="6" t="s">
+      <c r="F105" s="7"/>
+      <c r="G105" s="10" t="s">
         <v>307</v>
       </c>
-      <c r="H105" s="12" t="s">
+      <c r="H105" s="18" t="s">
         <v>426</v>
       </c>
-      <c r="I105" s="14"/>
-      <c r="K105" s="6"/>
-    </row>
-    <row r="106" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A106" s="6" t="s">
+      <c r="I105" s="12"/>
+      <c r="K105" s="10"/>
+    </row>
+    <row r="106" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A106" s="10" t="s">
         <v>310</v>
       </c>
-      <c r="B106" s="4" t="s">
+      <c r="B106" s="7" t="s">
         <v>248</v>
       </c>
-      <c r="C106" s="5" t="s">
+      <c r="C106" s="8" t="s">
         <v>296</v>
       </c>
       <c r="D106" s="9"/>
-      <c r="E106" s="4" t="s">
+      <c r="E106" s="7" t="s">
         <v>311</v>
       </c>
-      <c r="F106" s="4"/>
-      <c r="G106" s="6" t="s">
+      <c r="F106" s="7"/>
+      <c r="G106" s="10" t="s">
         <v>309</v>
       </c>
-      <c r="H106" s="11" t="s">
+      <c r="H106" s="17" t="s">
         <v>427</v>
       </c>
-      <c r="I106" s="14"/>
-      <c r="K106" s="6"/>
-    </row>
-    <row r="107" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A107" s="6" t="s">
+      <c r="I106" s="12"/>
+      <c r="K106" s="10"/>
+    </row>
+    <row r="107" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A107" s="10" t="s">
         <v>313</v>
       </c>
-      <c r="B107" s="4" t="s">
+      <c r="B107" s="7" t="s">
         <v>53</v>
       </c>
-      <c r="C107" s="5" t="s">
+      <c r="C107" s="8" t="s">
         <v>122</v>
       </c>
       <c r="D107" s="9"/>
-      <c r="E107" s="4" t="s">
+      <c r="E107" s="7" t="s">
         <v>43</v>
       </c>
-      <c r="F107" s="4"/>
-      <c r="G107" s="6" t="s">
+      <c r="F107" s="7"/>
+      <c r="G107" s="10" t="s">
         <v>312</v>
       </c>
-      <c r="H107" s="11" t="s">
+      <c r="H107" s="17" t="s">
         <v>428</v>
       </c>
-      <c r="I107" s="14"/>
-      <c r="K107" s="6"/>
-    </row>
-    <row r="108" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A108" s="6" t="s">
+      <c r="I107" s="12"/>
+      <c r="K107" s="10"/>
+    </row>
+    <row r="108" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A108" s="10" t="s">
         <v>429</v>
       </c>
-      <c r="C108" s="5">
+      <c r="C108" s="8">
         <v>220</v>
       </c>
-      <c r="E108" s="4">
+      <c r="E108" s="7">
         <v>22</v>
       </c>
-      <c r="G108" s="6" t="s">
+      <c r="G108" s="10" t="s">
         <v>435</v>
       </c>
-      <c r="H108" s="11" t="s">
+      <c r="H108" s="17" t="s">
         <v>432</v>
       </c>
-      <c r="I108" s="14"/>
-    </row>
-    <row r="109" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A109" s="6" t="s">
+      <c r="I108" s="12"/>
+    </row>
+    <row r="109" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A109" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="C109" s="5">
+      <c r="C109" s="8">
         <v>140</v>
       </c>
-      <c r="E109" s="4">
+      <c r="E109" s="7">
         <v>14</v>
       </c>
-      <c r="G109" s="6" t="s">
+      <c r="G109" s="10" t="s">
         <v>436</v>
       </c>
-      <c r="H109" s="11" t="s">
+      <c r="H109" s="17" t="s">
         <v>433</v>
       </c>
-      <c r="I109" s="14"/>
-    </row>
-    <row r="110" spans="1:11" s="7" customFormat="1" x14ac:dyDescent="0.2">
-      <c r="A110" s="13" t="s">
+      <c r="I109" s="12"/>
+    </row>
+    <row r="110" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A110" s="19" t="s">
         <v>431</v>
       </c>
-      <c r="C110" s="5">
+      <c r="C110" s="8">
         <v>230</v>
       </c>
-      <c r="E110" s="4">
+      <c r="E110" s="7">
         <v>23</v>
       </c>
-      <c r="G110" s="10" t="s">
+      <c r="G110" s="11" t="s">
         <v>437</v>
       </c>
-      <c r="H110" s="10" t="s">
+      <c r="H110" s="11" t="s">
         <v>434</v>
       </c>
-      <c r="I110" s="14"/>
-    </row>
-    <row r="111" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A111" s="13" t="s">
+      <c r="I110" s="12"/>
+    </row>
+    <row r="111" spans="1:11" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A111" s="19" t="s">
         <v>438</v>
       </c>
-      <c r="B111" s="7"/>
-      <c r="C111" s="5">
+      <c r="C111" s="8">
         <v>450</v>
       </c>
       <c r="D111" s="9">
         <v>430</v>
       </c>
-      <c r="E111" s="4">
+      <c r="E111" s="7">
         <v>45</v>
       </c>
-      <c r="F111" s="4">
+      <c r="F111" s="7">
         <v>45</v>
       </c>
-      <c r="G111" s="10" t="s">
+      <c r="G111" s="11" t="s">
         <v>439</v>
       </c>
-      <c r="H111" s="10" t="s">
+      <c r="H111" s="11" t="s">
         <v>440</v>
       </c>
-      <c r="I111" s="15"/>
+      <c r="I111" s="12"/>
     </row>
     <row r="112" spans="1:11" x14ac:dyDescent="0.2">
-      <c r="A112" s="20" t="s">
+      <c r="A112" s="5" t="s">
         <v>446</v>
       </c>
-      <c r="B112" s="18">
+      <c r="B112" s="3">
         <v>57.24</v>
       </c>
-      <c r="C112" s="18">
+      <c r="C112" s="3">
         <v>65</v>
       </c>
-      <c r="D112" s="18">
+      <c r="D112" s="3">
         <v>90</v>
       </c>
-      <c r="E112" s="18">
+      <c r="E112" s="3">
         <v>9</v>
       </c>
-      <c r="F112" s="18"/>
-      <c r="G112" s="19" t="s">
+      <c r="F112" s="3"/>
+      <c r="G112" s="4" t="s">
         <v>444</v>
       </c>
-      <c r="H112" s="19" t="s">
+      <c r="H112" s="4" t="s">
         <v>445</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A113" s="21" t="s">
+      <c r="A113" s="6" t="s">
         <v>447</v>
       </c>
-      <c r="B113" s="18">
+      <c r="B113" s="3">
         <v>129.30000000000001</v>
       </c>
-      <c r="C113" s="18">
+      <c r="C113" s="3">
         <v>160</v>
       </c>
-      <c r="D113" s="18">
+      <c r="D113" s="3">
         <v>155</v>
       </c>
-      <c r="E113" s="18">
+      <c r="E113" s="3">
         <v>16</v>
       </c>
-      <c r="F113" s="18"/>
-      <c r="G113" s="19" t="s">
+      <c r="F113" s="3"/>
+      <c r="G113" s="4" t="s">
         <v>448</v>
       </c>
-      <c r="H113" s="19" t="s">
+      <c r="H113" s="4" t="s">
         <v>449</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A114" s="21" t="s">
+      <c r="A114" s="6" t="s">
         <v>450</v>
       </c>
-      <c r="B114" s="18">
+      <c r="B114" s="3">
         <v>97</v>
       </c>
-      <c r="C114" s="18">
+      <c r="C114" s="3">
         <v>110</v>
       </c>
-      <c r="D114" s="18">
+      <c r="D114" s="3">
         <v>120</v>
       </c>
-      <c r="E114" s="18">
+      <c r="E114" s="3">
         <v>12</v>
       </c>
-      <c r="F114" s="18"/>
-      <c r="G114" s="19" t="s">
+      <c r="F114" s="3"/>
+      <c r="G114" s="4" t="s">
         <v>451</v>
       </c>
-      <c r="H114" s="19" t="s">
+      <c r="H114" s="4" t="s">
         <v>452</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A115" s="21" t="s">
+      <c r="A115" s="6" t="s">
         <v>453</v>
       </c>
-      <c r="B115" s="18">
+      <c r="B115" s="3">
         <v>263</v>
       </c>
-      <c r="C115" s="18">
+      <c r="C115" s="3">
         <v>350</v>
       </c>
-      <c r="D115" s="18"/>
-      <c r="E115" s="18">
+      <c r="D115" s="3"/>
+      <c r="E115" s="3">
         <v>35</v>
       </c>
-      <c r="F115" s="18"/>
-      <c r="G115" s="19" t="s">
+      <c r="F115" s="3"/>
+      <c r="G115" s="4" t="s">
         <v>454</v>
       </c>
-      <c r="H115" s="19" t="s">
+      <c r="H115" s="4" t="s">
         <v>455</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A116" s="21" t="s">
+      <c r="A116" s="6" t="s">
         <v>456</v>
       </c>
-      <c r="B116" s="18">
+      <c r="B116" s="3">
         <v>107.06</v>
       </c>
-      <c r="C116" s="18">
+      <c r="C116" s="3">
         <v>120</v>
       </c>
-      <c r="D116" s="18">
+      <c r="D116" s="3">
         <v>140</v>
       </c>
-      <c r="E116" s="18">
+      <c r="E116" s="3">
         <v>15</v>
       </c>
-      <c r="F116" s="18"/>
-      <c r="G116" s="19" t="s">
+      <c r="F116" s="3"/>
+      <c r="G116" s="4" t="s">
         <v>457</v>
       </c>
-      <c r="H116" s="19" t="s">
+      <c r="H116" s="4" t="s">
         <v>458</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A117" s="21" t="s">
+      <c r="A117" s="6" t="s">
         <v>459</v>
       </c>
-      <c r="B117" s="18">
+      <c r="B117" s="3">
         <v>201.4</v>
       </c>
-      <c r="C117" s="18">
+      <c r="C117" s="3">
         <v>230</v>
       </c>
-      <c r="D117" s="18"/>
-      <c r="E117" s="18">
+      <c r="D117" s="3"/>
+      <c r="E117" s="3">
         <v>23</v>
       </c>
-      <c r="F117" s="18"/>
-      <c r="G117" s="19" t="s">
+      <c r="F117" s="3"/>
+      <c r="G117" s="4" t="s">
         <v>460</v>
       </c>
-      <c r="H117" s="19" t="s">
+      <c r="H117" s="4" t="s">
         <v>461</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A118" s="21" t="s">
+      <c r="A118" s="6" t="s">
         <v>464</v>
       </c>
-      <c r="B118" s="18">
+      <c r="B118" s="3">
         <v>175</v>
       </c>
-      <c r="C118" s="18">
+      <c r="C118" s="3">
         <v>200</v>
       </c>
-      <c r="D118" s="18"/>
-      <c r="E118" s="18">
+      <c r="D118" s="3"/>
+      <c r="E118" s="3">
         <v>20</v>
       </c>
-      <c r="F118" s="18"/>
-      <c r="G118" s="19" t="s">
+      <c r="F118" s="3"/>
+      <c r="G118" s="4" t="s">
         <v>465</v>
       </c>
-      <c r="H118" s="19" t="s">
+      <c r="H118" s="4" t="s">
         <v>466</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A119" s="21" t="s">
+      <c r="A119" s="6" t="s">
         <v>476</v>
       </c>
-      <c r="B119" s="18">
+      <c r="B119" s="3">
         <v>466.4</v>
       </c>
-      <c r="C119" s="18">
+      <c r="C119" s="3">
         <v>560</v>
       </c>
-      <c r="D119" s="18"/>
-      <c r="E119" s="18">
+      <c r="D119" s="3"/>
+      <c r="E119" s="3">
         <v>56</v>
       </c>
-      <c r="F119" s="18"/>
-      <c r="G119" s="19" t="s">
+      <c r="F119" s="3"/>
+      <c r="G119" s="4" t="s">
         <v>467</v>
       </c>
-      <c r="H119" s="19" t="s">
+      <c r="H119" s="4" t="s">
         <v>468</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A120" s="21" t="s">
+      <c r="A120" s="6" t="s">
         <v>478</v>
       </c>
-      <c r="B120" s="18">
+      <c r="B120" s="3">
         <v>225</v>
       </c>
-      <c r="C120" s="18">
+      <c r="C120" s="3">
         <v>260</v>
       </c>
-      <c r="D120" s="18"/>
-      <c r="E120" s="18">
+      <c r="D120" s="3"/>
+      <c r="E120" s="3">
         <v>26</v>
       </c>
-      <c r="F120" s="18"/>
-      <c r="G120" s="19" t="s">
+      <c r="F120" s="3"/>
+      <c r="G120" s="4" t="s">
         <v>469</v>
       </c>
-      <c r="H120" s="19" t="s">
+      <c r="H120" s="4" t="s">
         <v>470</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A121" s="21" t="s">
+      <c r="A121" s="6" t="s">
         <v>477</v>
       </c>
-      <c r="B121" s="18">
+      <c r="B121" s="3">
         <v>175</v>
       </c>
-      <c r="C121" s="18">
+      <c r="C121" s="3">
         <v>200</v>
       </c>
-      <c r="D121" s="18"/>
-      <c r="E121" s="18">
+      <c r="D121" s="3"/>
+      <c r="E121" s="3">
         <v>20</v>
       </c>
-      <c r="F121" s="18"/>
-      <c r="G121" s="19" t="s">
+      <c r="F121" s="3"/>
+      <c r="G121" s="4" t="s">
         <v>471</v>
       </c>
-      <c r="H121" s="19" t="s">
+      <c r="H121" s="4" t="s">
         <v>472</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A122" s="21" t="s">
+      <c r="A122" s="6" t="s">
         <v>473</v>
       </c>
-      <c r="B122" s="18">
+      <c r="B122" s="3">
         <v>158</v>
       </c>
-      <c r="C122" s="18">
+      <c r="C122" s="3">
         <v>180</v>
       </c>
-      <c r="D122" s="18"/>
-      <c r="E122" s="18">
+      <c r="D122" s="3"/>
+      <c r="E122" s="3">
         <v>18</v>
       </c>
-      <c r="F122" s="18"/>
-      <c r="G122" s="19" t="s">
+      <c r="F122" s="3"/>
+      <c r="G122" s="4" t="s">
         <v>474</v>
       </c>
-      <c r="H122" s="19" t="s">
+      <c r="H122" s="4" t="s">
         <v>475</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A123" s="21" t="s">
+      <c r="A123" s="6" t="s">
         <v>479</v>
       </c>
-      <c r="B123" s="18">
+      <c r="B123" s="3">
         <v>424</v>
       </c>
-      <c r="C123" s="18">
+      <c r="C123" s="3">
         <v>500</v>
       </c>
-      <c r="D123" s="18"/>
-      <c r="E123" s="18">
+      <c r="D123" s="3"/>
+      <c r="E123" s="3">
         <v>50</v>
       </c>
-      <c r="F123" s="18"/>
-      <c r="G123" s="19" t="s">
+      <c r="F123" s="3"/>
+      <c r="G123" s="4" t="s">
         <v>480</v>
       </c>
-      <c r="H123" s="19" t="s">
+      <c r="H123" s="4" t="s">
         <v>481</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A124" s="21" t="s">
+      <c r="A124" s="6" t="s">
         <v>482</v>
       </c>
-      <c r="B124" s="18">
+      <c r="B124" s="3">
         <v>143.1</v>
       </c>
-      <c r="C124" s="18">
+      <c r="C124" s="3">
         <v>160</v>
       </c>
-      <c r="D124" s="18"/>
-      <c r="E124" s="18">
+      <c r="D124" s="3"/>
+      <c r="E124" s="3">
         <v>16</v>
       </c>
-      <c r="F124" s="18"/>
-      <c r="G124" s="19" t="s">
+      <c r="F124" s="3"/>
+      <c r="G124" s="4" t="s">
         <v>483</v>
       </c>
-      <c r="H124" s="19" t="s">
+      <c r="H124" s="4" t="s">
         <v>484</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A125" s="21" t="s">
+      <c r="A125" s="6" t="s">
         <v>485</v>
       </c>
-      <c r="B125" s="18">
+      <c r="B125" s="3">
         <v>175</v>
       </c>
-      <c r="C125" s="18">
+      <c r="C125" s="3">
         <v>200</v>
       </c>
-      <c r="D125" s="18"/>
-      <c r="E125" s="18">
+      <c r="D125" s="3"/>
+      <c r="E125" s="3">
         <v>20</v>
       </c>
-      <c r="F125" s="18"/>
-      <c r="G125" s="19" t="s">
+      <c r="F125" s="3"/>
+      <c r="G125" s="4" t="s">
         <v>486</v>
       </c>
-      <c r="H125" s="19" t="s">
+      <c r="H125" s="4" t="s">
         <v>487</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A126" s="21" t="s">
+      <c r="A126" s="6" t="s">
         <v>490</v>
       </c>
-      <c r="B126" s="18">
+      <c r="B126" s="3">
         <v>167.48</v>
       </c>
-      <c r="C126" s="18">
+      <c r="C126" s="3">
         <v>200</v>
       </c>
-      <c r="D126" s="18"/>
-      <c r="E126" s="18">
+      <c r="D126" s="3"/>
+      <c r="E126" s="3">
         <v>20</v>
       </c>
-      <c r="F126" s="18"/>
-      <c r="G126" s="19" t="s">
+      <c r="F126" s="3"/>
+      <c r="G126" s="4" t="s">
         <v>488</v>
       </c>
-      <c r="H126" s="19" t="s">
+      <c r="H126" s="4" t="s">
         <v>489</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A127" s="21" t="s">
+      <c r="A127" s="6" t="s">
         <v>491</v>
       </c>
-      <c r="B127" s="18">
+      <c r="B127" s="3">
         <v>139.91999999999999</v>
       </c>
-      <c r="C127" s="18">
+      <c r="C127" s="3">
         <v>160</v>
       </c>
-      <c r="D127" s="18"/>
-      <c r="E127" s="18">
+      <c r="D127" s="3"/>
+      <c r="E127" s="3">
         <v>16</v>
       </c>
-      <c r="F127" s="18"/>
-      <c r="G127" s="19" t="s">
+      <c r="F127" s="3"/>
+      <c r="G127" s="4" t="s">
         <v>492</v>
       </c>
-      <c r="H127" s="19" t="s">
+      <c r="H127" s="4" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A128" s="21" t="s">
+      <c r="A128" s="6" t="s">
         <v>494</v>
       </c>
-      <c r="B128" s="18">
+      <c r="B128" s="3">
         <v>263</v>
       </c>
-      <c r="C128" s="18">
+      <c r="C128" s="3">
         <v>300</v>
       </c>
-      <c r="D128" s="18"/>
-      <c r="E128" s="18">
+      <c r="D128" s="3"/>
+      <c r="E128" s="3">
         <v>30</v>
       </c>
-      <c r="F128" s="18"/>
-      <c r="G128" s="19" t="s">
+      <c r="F128" s="3"/>
+      <c r="G128" s="4" t="s">
         <v>495</v>
       </c>
-      <c r="H128" s="19" t="s">
+      <c r="H128" s="4" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A129" s="21" t="s">
+      <c r="A129" s="6" t="s">
         <v>497</v>
       </c>
-      <c r="B129" s="18">
+      <c r="B129" s="3">
         <v>381.6</v>
       </c>
-      <c r="C129" s="18">
+      <c r="C129" s="3">
         <v>450</v>
       </c>
-      <c r="D129" s="18"/>
-      <c r="E129" s="18">
+      <c r="D129" s="3"/>
+      <c r="E129" s="3">
         <v>45</v>
       </c>
-      <c r="F129" s="18"/>
-      <c r="G129" s="19" t="s">
+      <c r="F129" s="3"/>
+      <c r="G129" s="4" t="s">
         <v>499</v>
       </c>
-      <c r="H129" s="19" t="s">
+      <c r="H129" s="4" t="s">
         <v>498</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A130" s="21" t="s">
+      <c r="A130" s="6" t="s">
         <v>500</v>
       </c>
-      <c r="B130" s="18">
+      <c r="B130" s="3">
         <v>263</v>
       </c>
-      <c r="C130" s="18">
+      <c r="C130" s="3">
         <v>300</v>
       </c>
-      <c r="D130" s="18"/>
-      <c r="E130" s="18">
+      <c r="D130" s="3"/>
+      <c r="E130" s="3">
         <v>30</v>
       </c>
-      <c r="F130" s="18"/>
-      <c r="G130" s="19" t="s">
+      <c r="F130" s="3"/>
+      <c r="G130" s="4" t="s">
         <v>501</v>
       </c>
-      <c r="H130" s="19" t="s">
+      <c r="H130" s="4" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A131" s="21" t="s">
+      <c r="A131" s="6" t="s">
         <v>503</v>
       </c>
-      <c r="B131" s="18">
+      <c r="B131" s="3">
         <v>175</v>
       </c>
-      <c r="C131" s="18">
+      <c r="C131" s="3">
         <v>200</v>
       </c>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18">
+      <c r="D131" s="3"/>
+      <c r="E131" s="3">
         <v>20</v>
       </c>
-      <c r="F131" s="18"/>
-      <c r="G131" s="19" t="s">
+      <c r="F131" s="3"/>
+      <c r="G131" s="4" t="s">
         <v>504</v>
       </c>
-      <c r="H131" s="19" t="s">
+      <c r="H131" s="4" t="s">
         <v>505</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A132" s="21"/>
-      <c r="B132" s="18"/>
-      <c r="C132" s="18"/>
-      <c r="D132" s="18"/>
-      <c r="E132" s="18"/>
-      <c r="F132" s="18"/>
-      <c r="G132" s="19"/>
-      <c r="H132" s="19"/>
-    </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A133" s="21"/>
-      <c r="B133" s="18"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="18"/>
-      <c r="E133" s="18"/>
-      <c r="F133" s="18"/>
-      <c r="G133" s="19"/>
-      <c r="H133" s="19"/>
-    </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A134" s="21"/>
-      <c r="B134" s="18"/>
-      <c r="C134" s="18"/>
-      <c r="D134" s="18"/>
-      <c r="E134" s="18"/>
-      <c r="F134" s="18"/>
-      <c r="G134" s="19"/>
-      <c r="H134" s="19"/>
-    </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A135" s="21"/>
-      <c r="B135" s="18"/>
-      <c r="C135" s="18"/>
-      <c r="D135" s="18"/>
-      <c r="E135" s="18"/>
-      <c r="F135" s="18"/>
-      <c r="G135" s="19"/>
-      <c r="H135" s="19"/>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A136" s="21"/>
-      <c r="B136" s="18"/>
-      <c r="C136" s="18"/>
-      <c r="D136" s="18"/>
-      <c r="E136" s="18"/>
-      <c r="F136" s="18"/>
-      <c r="G136" s="19"/>
-      <c r="H136" s="19"/>
+    <row r="132" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A132" s="6" t="s">
+        <v>506</v>
+      </c>
+      <c r="B132" s="20">
+        <v>455.8</v>
+      </c>
+      <c r="C132" s="20">
+        <v>550</v>
+      </c>
+      <c r="D132" s="20"/>
+      <c r="E132" s="20">
+        <v>55</v>
+      </c>
+      <c r="F132" s="20"/>
+      <c r="G132" s="11" t="s">
+        <v>507</v>
+      </c>
+      <c r="H132" s="11" t="s">
+        <v>508</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A133" s="6" t="s">
+        <v>509</v>
+      </c>
+      <c r="B133" s="20">
+        <v>129.30000000000001</v>
+      </c>
+      <c r="C133" s="20">
+        <v>150</v>
+      </c>
+      <c r="D133" s="20"/>
+      <c r="E133" s="20">
+        <v>15</v>
+      </c>
+      <c r="F133" s="20"/>
+      <c r="G133" s="11" t="s">
+        <v>510</v>
+      </c>
+      <c r="H133" s="11" t="s">
+        <v>511</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A134" s="6" t="s">
+        <v>512</v>
+      </c>
+      <c r="B134" s="20">
+        <v>225</v>
+      </c>
+      <c r="C134" s="20">
+        <v>260</v>
+      </c>
+      <c r="D134" s="20"/>
+      <c r="E134" s="20">
+        <v>26</v>
+      </c>
+      <c r="F134" s="20"/>
+      <c r="G134" s="11" t="s">
+        <v>513</v>
+      </c>
+      <c r="H134" s="11" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A135" s="6" t="s">
+        <v>515</v>
+      </c>
+      <c r="B135" s="20">
+        <v>175</v>
+      </c>
+      <c r="C135" s="20">
+        <v>200</v>
+      </c>
+      <c r="D135" s="20"/>
+      <c r="E135" s="20">
+        <v>20</v>
+      </c>
+      <c r="F135" s="20"/>
+      <c r="G135" s="11" t="s">
+        <v>516</v>
+      </c>
+      <c r="H135" s="11" t="s">
+        <v>517</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A136" s="6" t="s">
+        <v>518</v>
+      </c>
+      <c r="B136" s="20">
+        <v>678</v>
+      </c>
+      <c r="C136" s="20">
+        <v>800</v>
+      </c>
+      <c r="D136" s="20"/>
+      <c r="E136" s="20">
+        <v>80</v>
+      </c>
+      <c r="F136" s="20"/>
+      <c r="G136" s="11" t="s">
+        <v>519</v>
+      </c>
+      <c r="H136" s="11" t="s">
+        <v>520</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5C95D63-E6FC-471D-B7D8-1CA9D4CC8618}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4EC5BD-1A6B-4DDC-9621-681E29EE674B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1706,10 +1706,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>七匹狼（锋芒细支）</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>6901028143554</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -1895,6 +1891,10 @@
   </si>
   <si>
     <t>6901028324618</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>七匹狼（锋芒）</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -5192,7 +5192,7 @@
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A119" s="6" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="B119" s="3">
         <v>466.4</v>
@@ -5214,7 +5214,7 @@
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A120" s="6" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B120" s="3">
         <v>225</v>
@@ -5236,7 +5236,7 @@
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A121" s="6" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="B121" s="3">
         <v>175</v>
@@ -5258,7 +5258,7 @@
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A122" s="6" t="s">
-        <v>473</v>
+        <v>520</v>
       </c>
       <c r="B122" s="3">
         <v>158</v>
@@ -5272,15 +5272,15 @@
       </c>
       <c r="F122" s="3"/>
       <c r="G122" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="H122" s="4" t="s">
         <v>474</v>
-      </c>
-      <c r="H122" s="4" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A123" s="6" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B123" s="3">
         <v>424</v>
@@ -5294,15 +5294,15 @@
       </c>
       <c r="F123" s="3"/>
       <c r="G123" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="H123" s="4" t="s">
         <v>480</v>
-      </c>
-      <c r="H123" s="4" t="s">
-        <v>481</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A124" s="6" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B124" s="3">
         <v>143.1</v>
@@ -5316,15 +5316,15 @@
       </c>
       <c r="F124" s="3"/>
       <c r="G124" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="H124" s="4" t="s">
         <v>483</v>
-      </c>
-      <c r="H124" s="4" t="s">
-        <v>484</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A125" s="6" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B125" s="3">
         <v>175</v>
@@ -5338,15 +5338,15 @@
       </c>
       <c r="F125" s="3"/>
       <c r="G125" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="H125" s="4" t="s">
         <v>486</v>
-      </c>
-      <c r="H125" s="4" t="s">
-        <v>487</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A126" s="6" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B126" s="3">
         <v>167.48</v>
@@ -5360,15 +5360,15 @@
       </c>
       <c r="F126" s="3"/>
       <c r="G126" s="4" t="s">
+        <v>487</v>
+      </c>
+      <c r="H126" s="4" t="s">
         <v>488</v>
-      </c>
-      <c r="H126" s="4" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="127" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A127" s="6" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B127" s="3">
         <v>139.91999999999999</v>
@@ -5382,15 +5382,15 @@
       </c>
       <c r="F127" s="3"/>
       <c r="G127" s="4" t="s">
+        <v>491</v>
+      </c>
+      <c r="H127" s="4" t="s">
         <v>492</v>
-      </c>
-      <c r="H127" s="4" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A128" s="6" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B128" s="3">
         <v>263</v>
@@ -5404,15 +5404,15 @@
       </c>
       <c r="F128" s="3"/>
       <c r="G128" s="4" t="s">
+        <v>494</v>
+      </c>
+      <c r="H128" s="4" t="s">
         <v>495</v>
-      </c>
-      <c r="H128" s="4" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A129" s="6" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B129" s="3">
         <v>381.6</v>
@@ -5426,15 +5426,15 @@
       </c>
       <c r="F129" s="3"/>
       <c r="G129" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H129" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A130" s="6" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B130" s="3">
         <v>263</v>
@@ -5448,15 +5448,15 @@
       </c>
       <c r="F130" s="3"/>
       <c r="G130" s="4" t="s">
+        <v>500</v>
+      </c>
+      <c r="H130" s="4" t="s">
         <v>501</v>
-      </c>
-      <c r="H130" s="4" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A131" s="6" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="B131" s="3">
         <v>175</v>
@@ -5470,15 +5470,15 @@
       </c>
       <c r="F131" s="3"/>
       <c r="G131" s="4" t="s">
+        <v>503</v>
+      </c>
+      <c r="H131" s="4" t="s">
         <v>504</v>
-      </c>
-      <c r="H131" s="4" t="s">
-        <v>505</v>
       </c>
     </row>
     <row r="132" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A132" s="6" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B132" s="20">
         <v>455.8</v>
@@ -5492,15 +5492,15 @@
       </c>
       <c r="F132" s="20"/>
       <c r="G132" s="11" t="s">
+        <v>506</v>
+      </c>
+      <c r="H132" s="11" t="s">
         <v>507</v>
-      </c>
-      <c r="H132" s="11" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="133" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A133" s="6" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B133" s="20">
         <v>129.30000000000001</v>
@@ -5514,15 +5514,15 @@
       </c>
       <c r="F133" s="20"/>
       <c r="G133" s="11" t="s">
+        <v>509</v>
+      </c>
+      <c r="H133" s="11" t="s">
         <v>510</v>
-      </c>
-      <c r="H133" s="11" t="s">
-        <v>511</v>
       </c>
     </row>
     <row r="134" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A134" s="6" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B134" s="20">
         <v>225</v>
@@ -5536,15 +5536,15 @@
       </c>
       <c r="F134" s="20"/>
       <c r="G134" s="11" t="s">
+        <v>512</v>
+      </c>
+      <c r="H134" s="11" t="s">
         <v>513</v>
-      </c>
-      <c r="H134" s="11" t="s">
-        <v>514</v>
       </c>
     </row>
     <row r="135" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A135" s="6" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B135" s="20">
         <v>175</v>
@@ -5558,15 +5558,15 @@
       </c>
       <c r="F135" s="20"/>
       <c r="G135" s="11" t="s">
+        <v>515</v>
+      </c>
+      <c r="H135" s="11" t="s">
         <v>516</v>
-      </c>
-      <c r="H135" s="11" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="136" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
       <c r="A136" s="6" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B136" s="20">
         <v>678</v>
@@ -5580,10 +5580,10 @@
       </c>
       <c r="F136" s="20"/>
       <c r="G136" s="11" t="s">
+        <v>518</v>
+      </c>
+      <c r="H136" s="11" t="s">
         <v>519</v>
-      </c>
-      <c r="H136" s="11" t="s">
-        <v>520</v>
       </c>
     </row>
   </sheetData>

--- a/烟草库存模板.xlsx
+++ b/烟草库存模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\XL\Desktop\dc\烟草价格查询\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB4EC5BD-1A6B-4DDC-9621-681E29EE674B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2AB6DD07-7601-4DCA-BEAC-EBF0CC83E2BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19440" windowHeight="14880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="521">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="723" uniqueCount="524">
   <si>
     <t>商品名称</t>
   </si>
@@ -1895,6 +1895,18 @@
   </si>
   <si>
     <t>七匹狼（锋芒）</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>8888075018616</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>8888075018609</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>555（双冰）</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -2346,7 +2358,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A80C0A3B-2542-45F0-B3D4-3E8698F6D850}">
-  <dimension ref="A1:K136"/>
+  <dimension ref="A1:K137"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="25" customWidth="1"/>
@@ -5586,6 +5598,28 @@
         <v>519</v>
       </c>
     </row>
+    <row r="137" spans="1:8" s="13" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A137" s="6" t="s">
+        <v>523</v>
+      </c>
+      <c r="B137" s="20">
+        <v>271.07</v>
+      </c>
+      <c r="C137" s="20">
+        <v>320</v>
+      </c>
+      <c r="D137" s="20"/>
+      <c r="E137" s="20">
+        <v>32</v>
+      </c>
+      <c r="F137" s="20"/>
+      <c r="G137" s="11" t="s">
+        <v>521</v>
+      </c>
+      <c r="H137" s="11" t="s">
+        <v>522</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
